--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_power.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_power.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1364707965524225</v>
+        <v>0.1361774666406967</v>
       </c>
       <c r="C2">
-        <v>175.887499956929</v>
+        <v>174.9296146533569</v>
       </c>
       <c r="D2">
-        <v>170.727499956929</v>
+        <v>171.2816146533569</v>
       </c>
       <c r="E2">
-        <v>-37.3</v>
+        <v>-35.788</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.512</v>
       </c>
       <c r="G2">
         <v>5.16</v>
@@ -1439,28 +1439,28 @@
         <v>18.825</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0760536</v>
       </c>
       <c r="N2">
-        <v>18.825</v>
+        <v>18.7489464</v>
       </c>
       <c r="O2">
-        <v>4.518</v>
+        <v>4.499747135999999</v>
       </c>
       <c r="P2">
-        <v>14.307</v>
+        <v>14.249199264</v>
       </c>
       <c r="Q2">
-        <v>22.107</v>
+        <v>22.049199264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1364707965524225</v>
+        <v>0.1371668551926229</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4489193649500481</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>247.5227997096784</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1361774666406967</v>
+        <v>0.1358841367289709</v>
       </c>
       <c r="C3">
-        <v>174.9296146533569</v>
+        <v>173.9753379410616</v>
       </c>
       <c r="D3">
-        <v>171.2816146533569</v>
+        <v>171.8393379410616</v>
       </c>
       <c r="E3">
-        <v>-35.788</v>
+        <v>-34.276</v>
       </c>
       <c r="F3">
-        <v>1.512</v>
+        <v>3.024</v>
       </c>
       <c r="G3">
         <v>5.16</v>
@@ -1521,28 +1521,28 @@
         <v>18.825</v>
       </c>
       <c r="M3">
-        <v>0.0760536</v>
+        <v>0.1521072</v>
       </c>
       <c r="N3">
-        <v>18.7489464</v>
+        <v>18.6728928</v>
       </c>
       <c r="O3">
-        <v>4.499747135999999</v>
+        <v>4.481494272</v>
       </c>
       <c r="P3">
-        <v>14.249199264</v>
+        <v>14.191398528</v>
       </c>
       <c r="Q3">
-        <v>22.049199264</v>
+        <v>21.991398528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1371668551926229</v>
+        <v>0.1378771191111948</v>
       </c>
       <c r="T3">
-        <v>0.4489193649500481</v>
+        <v>0.4524091559316901</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>247.5227997096784</v>
+        <v>123.7613998548392</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1358841367289709</v>
+        <v>0.1355908068172451</v>
       </c>
       <c r="C4">
-        <v>173.9753379410616</v>
+        <v>173.0247051858383</v>
       </c>
       <c r="D4">
-        <v>171.8393379410616</v>
+        <v>172.4007051858383</v>
       </c>
       <c r="E4">
-        <v>-34.276</v>
+        <v>-32.764</v>
       </c>
       <c r="F4">
-        <v>3.024</v>
+        <v>4.536</v>
       </c>
       <c r="G4">
         <v>5.16</v>
@@ -1603,28 +1603,28 @@
         <v>18.825</v>
       </c>
       <c r="M4">
-        <v>0.1521072</v>
+        <v>0.2281608</v>
       </c>
       <c r="N4">
-        <v>18.6728928</v>
+        <v>18.5968392</v>
       </c>
       <c r="O4">
-        <v>4.481494272</v>
+        <v>4.463241407999999</v>
       </c>
       <c r="P4">
-        <v>14.191398528</v>
+        <v>14.133597792</v>
       </c>
       <c r="Q4">
-        <v>21.991398528</v>
+        <v>21.933597792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1378771191111948</v>
+        <v>0.1386020276466444</v>
       </c>
       <c r="T4">
-        <v>0.4524091559316901</v>
+        <v>0.4559709013665619</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.7613998548392</v>
+        <v>82.50759990322615</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1355908068172451</v>
+        <v>0.1352974769055193</v>
       </c>
       <c r="C5">
-        <v>173.0247051858383</v>
+        <v>172.0777522171307</v>
       </c>
       <c r="D5">
-        <v>172.4007051858383</v>
+        <v>172.9657522171307</v>
       </c>
       <c r="E5">
-        <v>-32.764</v>
+        <v>-31.252</v>
       </c>
       <c r="F5">
-        <v>4.536</v>
+        <v>6.048</v>
       </c>
       <c r="G5">
         <v>5.16</v>
@@ -1685,28 +1685,28 @@
         <v>18.825</v>
       </c>
       <c r="M5">
-        <v>0.2281608</v>
+        <v>0.3042144</v>
       </c>
       <c r="N5">
-        <v>18.5968392</v>
+        <v>18.5207856</v>
       </c>
       <c r="O5">
-        <v>4.463241407999999</v>
+        <v>4.444988544</v>
       </c>
       <c r="P5">
-        <v>14.133597792</v>
+        <v>14.075797056</v>
       </c>
       <c r="Q5">
-        <v>21.933597792</v>
+        <v>21.875797056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1386020276466444</v>
+        <v>0.1393420384432493</v>
       </c>
       <c r="T5">
-        <v>0.4559709013665619</v>
+        <v>0.4596068498313268</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.50759990322615</v>
+        <v>61.88069992741961</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1352974769055193</v>
+        <v>0.1350041469937935</v>
       </c>
       <c r="C6">
-        <v>172.0777522171307</v>
+        <v>171.1345153356545</v>
       </c>
       <c r="D6">
-        <v>172.9657522171307</v>
+        <v>173.5345153356545</v>
       </c>
       <c r="E6">
-        <v>-31.252</v>
+        <v>-29.74</v>
       </c>
       <c r="F6">
-        <v>6.048</v>
+        <v>7.56</v>
       </c>
       <c r="G6">
         <v>5.16</v>
@@ -1767,28 +1767,28 @@
         <v>18.825</v>
       </c>
       <c r="M6">
-        <v>0.3042144</v>
+        <v>0.3802679999999999</v>
       </c>
       <c r="N6">
-        <v>18.5207856</v>
+        <v>18.444732</v>
       </c>
       <c r="O6">
-        <v>4.444988544</v>
+        <v>4.426735679999999</v>
       </c>
       <c r="P6">
-        <v>14.075797056</v>
+        <v>14.01799632</v>
       </c>
       <c r="Q6">
-        <v>21.875797056</v>
+        <v>21.81799632</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1393420384432493</v>
+        <v>0.1400976284145194</v>
       </c>
       <c r="T6">
-        <v>0.4596068498313268</v>
+        <v>0.4633193445795605</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.88069992741961</v>
+        <v>49.50455994193569</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1350041469937935</v>
+        <v>0.1347108170820677</v>
       </c>
       <c r="C7">
-        <v>171.1345153356545</v>
+        <v>170.1950313211707</v>
       </c>
       <c r="D7">
-        <v>173.5345153356545</v>
+        <v>174.1070313211707</v>
       </c>
       <c r="E7">
-        <v>-29.74</v>
+        <v>-28.228</v>
       </c>
       <c r="F7">
-        <v>7.56</v>
+        <v>9.071999999999999</v>
       </c>
       <c r="G7">
         <v>5.16</v>
@@ -1849,28 +1849,28 @@
         <v>18.825</v>
       </c>
       <c r="M7">
-        <v>0.3802679999999999</v>
+        <v>0.4563215999999999</v>
       </c>
       <c r="N7">
-        <v>18.444732</v>
+        <v>18.3686784</v>
       </c>
       <c r="O7">
-        <v>4.426735679999999</v>
+        <v>4.408482816</v>
       </c>
       <c r="P7">
-        <v>14.01799632</v>
+        <v>13.960195584</v>
       </c>
       <c r="Q7">
-        <v>21.81799632</v>
+        <v>21.760195584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1400976284145194</v>
+        <v>0.1408692947681571</v>
       </c>
       <c r="T7">
-        <v>0.4633193445795605</v>
+        <v>0.4671108285777565</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.50455994193569</v>
+        <v>41.25379995161308</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1347108170820677</v>
+        <v>0.1344174871703419</v>
       </c>
       <c r="C8">
-        <v>170.1950313211707</v>
+        <v>169.2593374404146</v>
       </c>
       <c r="D8">
-        <v>174.1070313211707</v>
+        <v>174.6833374404146</v>
       </c>
       <c r="E8">
-        <v>-28.228</v>
+        <v>-26.716</v>
       </c>
       <c r="F8">
-        <v>9.071999999999999</v>
+        <v>10.584</v>
       </c>
       <c r="G8">
         <v>5.16</v>
@@ -1931,28 +1931,28 @@
         <v>18.825</v>
       </c>
       <c r="M8">
-        <v>0.4563215999999999</v>
+        <v>0.5323751999999998</v>
       </c>
       <c r="N8">
-        <v>18.3686784</v>
+        <v>18.2926248</v>
       </c>
       <c r="O8">
-        <v>4.408482816</v>
+        <v>4.390229951999999</v>
       </c>
       <c r="P8">
-        <v>13.960195584</v>
+        <v>13.902394848</v>
       </c>
       <c r="Q8">
-        <v>21.760195584</v>
+        <v>21.702394848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1408692947681571</v>
+        <v>0.1416575560971418</v>
       </c>
       <c r="T8">
-        <v>0.4671108285777565</v>
+        <v>0.4709838498662364</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.25379995161308</v>
+        <v>35.3603999585255</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1344174871703418</v>
+        <v>0.134124157258616</v>
       </c>
       <c r="C9">
-        <v>169.2593374404146</v>
+        <v>168.3274714551818</v>
       </c>
       <c r="D9">
-        <v>174.6833374404146</v>
+        <v>175.2634714551818</v>
       </c>
       <c r="E9">
-        <v>-26.716</v>
+        <v>-25.204</v>
       </c>
       <c r="F9">
-        <v>10.584</v>
+        <v>12.096</v>
       </c>
       <c r="G9">
         <v>5.16</v>
@@ -2013,28 +2013,28 @@
         <v>18.825</v>
       </c>
       <c r="M9">
-        <v>0.5323751999999999</v>
+        <v>0.6084288</v>
       </c>
       <c r="N9">
-        <v>18.2926248</v>
+        <v>18.2165712</v>
       </c>
       <c r="O9">
-        <v>4.390229951999999</v>
+        <v>4.371977088</v>
       </c>
       <c r="P9">
-        <v>13.902394848</v>
+        <v>13.844594112</v>
       </c>
       <c r="Q9">
-        <v>21.702394848</v>
+        <v>21.644594112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1416575560971418</v>
+        <v>0.1424629535419739</v>
       </c>
       <c r="T9">
-        <v>0.4709838498662364</v>
+        <v>0.4749410672696832</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.36039995852549</v>
+        <v>30.94034996370981</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.134124157258616</v>
+        <v>0.1338308273468902</v>
       </c>
       <c r="C10">
-        <v>168.3274714551818</v>
+        <v>167.3994716305762</v>
       </c>
       <c r="D10">
-        <v>175.2634714551818</v>
+        <v>175.8474716305762</v>
       </c>
       <c r="E10">
-        <v>-25.204</v>
+        <v>-23.692</v>
       </c>
       <c r="F10">
-        <v>12.096</v>
+        <v>13.608</v>
       </c>
       <c r="G10">
         <v>5.16</v>
@@ -2095,28 +2095,28 @@
         <v>18.825</v>
       </c>
       <c r="M10">
-        <v>0.6084288</v>
+        <v>0.6844823999999999</v>
       </c>
       <c r="N10">
-        <v>18.2165712</v>
+        <v>18.1405176</v>
       </c>
       <c r="O10">
-        <v>4.371977088</v>
+        <v>4.353724224</v>
       </c>
       <c r="P10">
-        <v>13.844594112</v>
+        <v>13.786793376</v>
       </c>
       <c r="Q10">
-        <v>21.644594112</v>
+        <v>21.586793376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1424629535419739</v>
+        <v>0.1432860520295497</v>
       </c>
       <c r="T10">
-        <v>0.4749410672696832</v>
+        <v>0.4789852564841948</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.94034996370981</v>
+        <v>27.50253330107538</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1338308273468902</v>
+        <v>0.1335374974351644</v>
       </c>
       <c r="C11">
-        <v>167.3994716305762</v>
+        <v>166.4753767434241</v>
       </c>
       <c r="D11">
-        <v>175.8474716305762</v>
+        <v>176.4353767434241</v>
       </c>
       <c r="E11">
-        <v>-23.692</v>
+        <v>-22.18</v>
       </c>
       <c r="F11">
-        <v>13.608</v>
+        <v>15.12</v>
       </c>
       <c r="G11">
         <v>5.16</v>
@@ -2177,28 +2177,28 @@
         <v>18.825</v>
       </c>
       <c r="M11">
-        <v>0.6844823999999999</v>
+        <v>0.7605359999999999</v>
       </c>
       <c r="N11">
-        <v>18.1405176</v>
+        <v>18.064464</v>
       </c>
       <c r="O11">
-        <v>4.353724224</v>
+        <v>4.33547136</v>
       </c>
       <c r="P11">
-        <v>13.786793376</v>
+        <v>13.72899264</v>
       </c>
       <c r="Q11">
-        <v>21.586793376</v>
+        <v>21.52899264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1432860520295497</v>
+        <v>0.1441274415946271</v>
       </c>
       <c r="T11">
-        <v>0.4789852564841948</v>
+        <v>0.48311931657014</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.50253330107538</v>
+        <v>24.75227997096785</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1335374974351644</v>
+        <v>0.1332441675234386</v>
       </c>
       <c r="C12">
-        <v>166.4753767434241</v>
+        <v>165.5552260908558</v>
       </c>
       <c r="D12">
-        <v>176.4353767434241</v>
+        <v>177.0272260908558</v>
       </c>
       <c r="E12">
-        <v>-22.18</v>
+        <v>-20.668</v>
       </c>
       <c r="F12">
-        <v>15.12</v>
+        <v>16.632</v>
       </c>
       <c r="G12">
         <v>5.16</v>
@@ -2259,28 +2259,28 @@
         <v>18.825</v>
       </c>
       <c r="M12">
-        <v>0.7605359999999999</v>
+        <v>0.8365895999999998</v>
       </c>
       <c r="N12">
-        <v>18.064464</v>
+        <v>17.9884104</v>
       </c>
       <c r="O12">
-        <v>4.33547136</v>
+        <v>4.317218496</v>
       </c>
       <c r="P12">
-        <v>13.72899264</v>
+        <v>13.671191904</v>
       </c>
       <c r="Q12">
-        <v>21.52899264</v>
+        <v>21.471191904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1441274415946271</v>
+        <v>0.1449877387903804</v>
       </c>
       <c r="T12">
-        <v>0.48311931657014</v>
+        <v>0.4873462768827356</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.75227997096785</v>
+        <v>22.50207270087986</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1332441675234386</v>
+        <v>0.1329508376117128</v>
       </c>
       <c r="C13">
-        <v>165.5552260908558</v>
+        <v>164.6390594990629</v>
       </c>
       <c r="D13">
-        <v>177.0272260908558</v>
+        <v>177.6230594990629</v>
       </c>
       <c r="E13">
-        <v>-20.668</v>
+        <v>-19.156</v>
       </c>
       <c r="F13">
-        <v>16.632</v>
+        <v>18.144</v>
       </c>
       <c r="G13">
         <v>5.16</v>
@@ -2341,28 +2341,28 @@
         <v>18.825</v>
       </c>
       <c r="M13">
-        <v>0.8365895999999998</v>
+        <v>0.9126431999999999</v>
       </c>
       <c r="N13">
-        <v>17.9884104</v>
+        <v>17.9123568</v>
       </c>
       <c r="O13">
-        <v>4.317218496</v>
+        <v>4.298965631999999</v>
       </c>
       <c r="P13">
-        <v>13.671191904</v>
+        <v>13.613391168</v>
       </c>
       <c r="Q13">
-        <v>21.471191904</v>
+        <v>21.413391168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1449877387903804</v>
+        <v>0.1458675881951282</v>
       </c>
       <c r="T13">
-        <v>0.4873462768827356</v>
+        <v>0.4916693044751629</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.50207270087986</v>
+        <v>20.62689997580654</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1329508376117128</v>
+        <v>0.132657507699987</v>
       </c>
       <c r="C14">
-        <v>164.6390594990629</v>
+        <v>163.7269173322314</v>
       </c>
       <c r="D14">
-        <v>177.6230594990629</v>
+        <v>178.2229173322314</v>
       </c>
       <c r="E14">
-        <v>-19.156</v>
+        <v>-17.644</v>
       </c>
       <c r="F14">
-        <v>18.144</v>
+        <v>19.656</v>
       </c>
       <c r="G14">
         <v>5.16</v>
@@ -2423,28 +2423,28 @@
         <v>18.825</v>
       </c>
       <c r="M14">
-        <v>0.9126431999999999</v>
+        <v>0.9886967999999999</v>
       </c>
       <c r="N14">
-        <v>17.9123568</v>
+        <v>17.8363032</v>
       </c>
       <c r="O14">
-        <v>4.298965631999999</v>
+        <v>4.280712768</v>
       </c>
       <c r="P14">
-        <v>13.613391168</v>
+        <v>13.555590432</v>
       </c>
       <c r="Q14">
-        <v>21.413391168</v>
+        <v>21.355590432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1458675881951282</v>
+        <v>0.1467676640229735</v>
       </c>
       <c r="T14">
-        <v>0.4916693044751629</v>
+        <v>0.4960917120122438</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.62689997580654</v>
+        <v>19.04021536228296</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.132657507699987</v>
+        <v>0.1323641777882612</v>
       </c>
       <c r="C15">
-        <v>163.7269173322314</v>
+        <v>162.8188405016567</v>
       </c>
       <c r="D15">
-        <v>178.2229173322314</v>
+        <v>178.8268405016567</v>
       </c>
       <c r="E15">
-        <v>-17.644</v>
+        <v>-16.132</v>
       </c>
       <c r="F15">
-        <v>19.656</v>
+        <v>21.168</v>
       </c>
       <c r="G15">
         <v>5.16</v>
@@ -2505,28 +2505,28 @@
         <v>18.825</v>
       </c>
       <c r="M15">
-        <v>0.9886967999999999</v>
+        <v>1.0647504</v>
       </c>
       <c r="N15">
-        <v>17.8363032</v>
+        <v>17.7602496</v>
       </c>
       <c r="O15">
-        <v>4.280712768</v>
+        <v>4.262459903999999</v>
       </c>
       <c r="P15">
-        <v>13.555590432</v>
+        <v>13.497789696</v>
       </c>
       <c r="Q15">
-        <v>21.355590432</v>
+        <v>21.297789696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1467676640229735</v>
+        <v>0.1476886718468153</v>
       </c>
       <c r="T15">
-        <v>0.4960917120122438</v>
+        <v>0.5006169662362334</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.04021536228296</v>
+        <v>17.68019997926275</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1323641777882612</v>
+        <v>0.1320708478765353</v>
       </c>
       <c r="C16">
-        <v>162.8188405016567</v>
+        <v>161.914870475045</v>
       </c>
       <c r="D16">
-        <v>178.8268405016567</v>
+        <v>179.434870475045</v>
       </c>
       <c r="E16">
-        <v>-16.132</v>
+        <v>-14.61999999999999</v>
       </c>
       <c r="F16">
-        <v>21.168</v>
+        <v>22.68</v>
       </c>
       <c r="G16">
         <v>5.16</v>
@@ -2587,28 +2587,28 @@
         <v>18.825</v>
       </c>
       <c r="M16">
-        <v>1.0647504</v>
+        <v>1.140804</v>
       </c>
       <c r="N16">
-        <v>17.7602496</v>
+        <v>17.684196</v>
       </c>
       <c r="O16">
-        <v>4.262459903999999</v>
+        <v>4.24420704</v>
       </c>
       <c r="P16">
-        <v>13.497789696</v>
+        <v>13.43998896</v>
       </c>
       <c r="Q16">
-        <v>21.297789696</v>
+        <v>21.23998896</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1476886718468153</v>
+        <v>0.1486313504429828</v>
       </c>
       <c r="T16">
-        <v>0.5006169662362334</v>
+        <v>0.5052486970301995</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.68019997926275</v>
+        <v>16.50151998064523</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1320708478765353</v>
+        <v>0.1317775179648095</v>
       </c>
       <c r="C17">
-        <v>161.9148704750451</v>
+        <v>161.0150492860049</v>
       </c>
       <c r="D17">
-        <v>179.4348704750451</v>
+        <v>180.0470492860049</v>
       </c>
       <c r="E17">
-        <v>-14.62</v>
+        <v>-13.108</v>
       </c>
       <c r="F17">
-        <v>22.68</v>
+        <v>24.192</v>
       </c>
       <c r="G17">
         <v>5.16</v>
@@ -2669,28 +2669,28 @@
         <v>18.825</v>
       </c>
       <c r="M17">
-        <v>1.140804</v>
+        <v>1.2168576</v>
       </c>
       <c r="N17">
-        <v>17.684196</v>
+        <v>17.6081424</v>
       </c>
       <c r="O17">
-        <v>4.24420704</v>
+        <v>4.225954175999999</v>
       </c>
       <c r="P17">
-        <v>13.43998896</v>
+        <v>13.382188224</v>
       </c>
       <c r="Q17">
-        <v>21.23998896</v>
+        <v>21.182188224</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1486313504429827</v>
+        <v>0.1495964737676304</v>
       </c>
       <c r="T17">
-        <v>0.5052486970301994</v>
+        <v>0.5099907071287836</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.50151998064523</v>
+        <v>15.4701749818549</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1317775179648095</v>
+        <v>0.1314841880530837</v>
       </c>
       <c r="C18">
-        <v>161.0150492860049</v>
+        <v>160.1194195437336</v>
       </c>
       <c r="D18">
-        <v>180.0470492860049</v>
+        <v>180.6634195437337</v>
       </c>
       <c r="E18">
-        <v>-13.108</v>
+        <v>-11.596</v>
       </c>
       <c r="F18">
-        <v>24.192</v>
+        <v>25.704</v>
       </c>
       <c r="G18">
         <v>5.16</v>
@@ -2751,28 +2751,28 @@
         <v>18.825</v>
       </c>
       <c r="M18">
-        <v>1.2168576</v>
+        <v>1.2929112</v>
       </c>
       <c r="N18">
-        <v>17.6081424</v>
+        <v>17.5320888</v>
       </c>
       <c r="O18">
-        <v>4.225954175999999</v>
+        <v>4.207701312</v>
       </c>
       <c r="P18">
-        <v>13.382188224</v>
+        <v>13.324387488</v>
       </c>
       <c r="Q18">
-        <v>21.182188224</v>
+        <v>21.124387488</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1495964737676304</v>
+        <v>0.1505848530760045</v>
       </c>
       <c r="T18">
-        <v>0.5099907071287836</v>
+        <v>0.5148469825309481</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.4701749818549</v>
+        <v>14.56016468880461</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1314841880530837</v>
+        <v>0.1311908581413579</v>
       </c>
       <c r="C19">
-        <v>160.1194195437336</v>
+        <v>159.2280244429035</v>
       </c>
       <c r="D19">
-        <v>180.6634195437337</v>
+        <v>181.2840244429036</v>
       </c>
       <c r="E19">
-        <v>-11.596</v>
+        <v>-10.084</v>
       </c>
       <c r="F19">
-        <v>25.704</v>
+        <v>27.216</v>
       </c>
       <c r="G19">
         <v>5.16</v>
@@ -2833,28 +2833,28 @@
         <v>18.825</v>
       </c>
       <c r="M19">
-        <v>1.2929112</v>
+        <v>1.3689648</v>
       </c>
       <c r="N19">
-        <v>17.5320888</v>
+        <v>17.4560352</v>
       </c>
       <c r="O19">
-        <v>4.207701312</v>
+        <v>4.189448447999999</v>
       </c>
       <c r="P19">
-        <v>13.324387488</v>
+        <v>13.266586752</v>
       </c>
       <c r="Q19">
-        <v>21.124387488</v>
+        <v>21.066586752</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1505848530760045</v>
+        <v>0.1515973391967779</v>
       </c>
       <c r="T19">
-        <v>0.5148469825309481</v>
+        <v>0.5198217036746289</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.56016468880461</v>
+        <v>13.75126665053769</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1311908581413579</v>
+        <v>0.1308975282296321</v>
       </c>
       <c r="C20">
-        <v>159.2280244429035</v>
+        <v>158.3409077737524</v>
       </c>
       <c r="D20">
-        <v>181.2840244429036</v>
+        <v>181.9089077737524</v>
       </c>
       <c r="E20">
-        <v>-10.084</v>
+        <v>-8.571999999999999</v>
       </c>
       <c r="F20">
-        <v>27.216</v>
+        <v>28.728</v>
       </c>
       <c r="G20">
         <v>5.16</v>
@@ -2915,28 +2915,28 @@
         <v>18.825</v>
       </c>
       <c r="M20">
-        <v>1.3689648</v>
+        <v>1.4450184</v>
       </c>
       <c r="N20">
-        <v>17.4560352</v>
+        <v>17.3799816</v>
       </c>
       <c r="O20">
-        <v>4.189448447999999</v>
+        <v>4.171195584</v>
       </c>
       <c r="P20">
-        <v>13.266586752</v>
+        <v>13.208786016</v>
       </c>
       <c r="Q20">
-        <v>21.066586752</v>
+        <v>21.008786016</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1515973391967779</v>
+        <v>0.1526348249748544</v>
       </c>
       <c r="T20">
-        <v>0.5198217036746288</v>
+        <v>0.5249192574391411</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.75126665053769</v>
+        <v>13.0275157741936</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1308975282296321</v>
+        <v>0.1308321983179063</v>
       </c>
       <c r="C21">
-        <v>158.3409077737524</v>
+        <v>156.9686676896676</v>
       </c>
       <c r="D21">
-        <v>181.9089077737524</v>
+        <v>182.0486676896676</v>
       </c>
       <c r="E21">
-        <v>-8.571999999999999</v>
+        <v>-7.059999999999999</v>
       </c>
       <c r="F21">
-        <v>28.728</v>
+        <v>30.24</v>
       </c>
       <c r="G21">
         <v>5.16</v>
@@ -2997,45 +2997,45 @@
         <v>18.825</v>
       </c>
       <c r="M21">
-        <v>1.4450184</v>
+        <v>1.566432</v>
       </c>
       <c r="N21">
-        <v>17.3799816</v>
+        <v>17.258568</v>
       </c>
       <c r="O21">
-        <v>4.171195584</v>
+        <v>4.14205632</v>
       </c>
       <c r="P21">
-        <v>13.208786016</v>
+        <v>13.11651168</v>
       </c>
       <c r="Q21">
-        <v>21.008786016</v>
+        <v>20.91651168</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1526348249748544</v>
+        <v>0.1536982478973828</v>
       </c>
       <c r="T21">
-        <v>0.5249192574391411</v>
+        <v>0.5301442500477662</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.0275157741936</v>
+        <v>12.01775755347184</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1308321983179063</v>
+        <v>0.1305502684061804</v>
       </c>
       <c r="C22">
-        <v>156.9686676896676</v>
+        <v>156.062270076265</v>
       </c>
       <c r="D22">
-        <v>182.0486676896676</v>
+        <v>182.654270076265</v>
       </c>
       <c r="E22">
-        <v>-7.059999999999999</v>
+        <v>-5.547999999999998</v>
       </c>
       <c r="F22">
-        <v>30.24</v>
+        <v>31.752</v>
       </c>
       <c r="G22">
         <v>5.16</v>
@@ -3079,28 +3079,28 @@
         <v>18.825</v>
       </c>
       <c r="M22">
-        <v>1.566432</v>
+        <v>1.6447536</v>
       </c>
       <c r="N22">
-        <v>17.258568</v>
+        <v>17.1802464</v>
       </c>
       <c r="O22">
-        <v>4.14205632</v>
+        <v>4.123259136</v>
       </c>
       <c r="P22">
-        <v>13.11651168</v>
+        <v>13.056987264</v>
       </c>
       <c r="Q22">
-        <v>20.91651168</v>
+        <v>20.856987264</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1536982478973828</v>
+        <v>0.1547885929192158</v>
       </c>
       <c r="T22">
-        <v>0.5301442500477662</v>
+        <v>0.5355015209502807</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.01775755347184</v>
+        <v>11.44548338425889</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1305502684061804</v>
+        <v>0.1302683384944547</v>
       </c>
       <c r="C23">
-        <v>156.062270076265</v>
+        <v>155.1599151001495</v>
       </c>
       <c r="D23">
-        <v>182.654270076265</v>
+        <v>183.2639151001495</v>
       </c>
       <c r="E23">
-        <v>-5.548000000000002</v>
+        <v>-4.036000000000001</v>
       </c>
       <c r="F23">
-        <v>31.752</v>
+        <v>33.264</v>
       </c>
       <c r="G23">
         <v>5.16</v>
@@ -3161,28 +3161,28 @@
         <v>18.825</v>
       </c>
       <c r="M23">
-        <v>1.6447536</v>
+        <v>1.7230752</v>
       </c>
       <c r="N23">
-        <v>17.1802464</v>
+        <v>17.1019248</v>
       </c>
       <c r="O23">
-        <v>4.123259136</v>
+        <v>4.104461951999999</v>
       </c>
       <c r="P23">
-        <v>13.056987264</v>
+        <v>12.997462848</v>
       </c>
       <c r="Q23">
-        <v>20.856987264</v>
+        <v>20.797462848</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1547885929192158</v>
+        <v>0.1559068955057111</v>
       </c>
       <c r="T23">
-        <v>0.5355015209502807</v>
+        <v>0.5409961577733724</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.44548338425889</v>
+        <v>10.92523413951985</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1302683384944547</v>
+        <v>0.1299864085827288</v>
       </c>
       <c r="C24">
-        <v>155.1599151001495</v>
+        <v>154.2616433762042</v>
       </c>
       <c r="D24">
-        <v>183.2639151001495</v>
+        <v>183.8776433762042</v>
       </c>
       <c r="E24">
-        <v>-4.036000000000001</v>
+        <v>-2.524000000000001</v>
       </c>
       <c r="F24">
-        <v>33.264</v>
+        <v>34.776</v>
       </c>
       <c r="G24">
         <v>5.16</v>
@@ -3243,28 +3243,28 @@
         <v>18.825</v>
       </c>
       <c r="M24">
-        <v>1.7230752</v>
+        <v>1.8013968</v>
       </c>
       <c r="N24">
-        <v>17.1019248</v>
+        <v>17.0236032</v>
       </c>
       <c r="O24">
-        <v>4.104461951999999</v>
+        <v>4.085664768</v>
       </c>
       <c r="P24">
-        <v>12.997462848</v>
+        <v>12.937938432</v>
       </c>
       <c r="Q24">
-        <v>20.797462848</v>
+        <v>20.737938432</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1559068955057111</v>
+        <v>0.1570542449126348</v>
       </c>
       <c r="T24">
-        <v>0.5409961577733724</v>
+        <v>0.5466335124360249</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.92523413951985</v>
+        <v>10.45022395954073</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1299864085827288</v>
+        <v>0.129704478671003</v>
       </c>
       <c r="C25">
-        <v>154.2616433762042</v>
+        <v>153.3674960651969</v>
       </c>
       <c r="D25">
-        <v>183.8776433762042</v>
+        <v>184.4954960651969</v>
       </c>
       <c r="E25">
-        <v>-2.524000000000001</v>
+        <v>-1.012</v>
       </c>
       <c r="F25">
-        <v>34.776</v>
+        <v>36.288</v>
       </c>
       <c r="G25">
         <v>5.16</v>
@@ -3325,28 +3325,28 @@
         <v>18.825</v>
       </c>
       <c r="M25">
-        <v>1.8013968</v>
+        <v>1.8797184</v>
       </c>
       <c r="N25">
-        <v>17.0236032</v>
+        <v>16.9452816</v>
       </c>
       <c r="O25">
-        <v>4.085664768</v>
+        <v>4.066867584000001</v>
       </c>
       <c r="P25">
-        <v>12.937938432</v>
+        <v>12.878414016</v>
       </c>
       <c r="Q25">
-        <v>20.737938432</v>
+        <v>20.678414016</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1570542449126348</v>
+        <v>0.158231787725004</v>
       </c>
       <c r="T25">
-        <v>0.5466335124360249</v>
+        <v>0.5524192185371682</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.45022395954073</v>
+        <v>10.01479796122653</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.129704478671003</v>
+        <v>0.1297455487592772</v>
       </c>
       <c r="C26">
-        <v>153.3674960651969</v>
+        <v>151.7652322403536</v>
       </c>
       <c r="D26">
-        <v>184.4954960651969</v>
+        <v>184.4052322403536</v>
       </c>
       <c r="E26">
-        <v>-1.012</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>36.288</v>
+        <v>37.8</v>
       </c>
       <c r="G26">
         <v>5.16</v>
@@ -3407,45 +3407,45 @@
         <v>18.825</v>
       </c>
       <c r="M26">
-        <v>1.8797184</v>
+        <v>2.0223</v>
       </c>
       <c r="N26">
-        <v>16.9452816</v>
+        <v>16.8027</v>
       </c>
       <c r="O26">
-        <v>4.066867584000001</v>
+        <v>4.032647999999999</v>
       </c>
       <c r="P26">
-        <v>12.878414016</v>
+        <v>12.770052</v>
       </c>
       <c r="Q26">
-        <v>20.678414016</v>
+        <v>20.570052</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.158231787725004</v>
+        <v>0.1594407316790362</v>
       </c>
       <c r="T26">
-        <v>0.5524192185371682</v>
+        <v>0.5583592101343421</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.01479796122653</v>
+        <v>9.308707906838746</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1297455487592772</v>
+        <v>0.1294765388475514</v>
       </c>
       <c r="C27">
-        <v>151.7652322403536</v>
+        <v>150.8460726700603</v>
       </c>
       <c r="D27">
-        <v>184.4052322403536</v>
+        <v>184.9980726700603</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>2.012</v>
       </c>
       <c r="F27">
-        <v>37.8</v>
+        <v>39.312</v>
       </c>
       <c r="G27">
         <v>5.16</v>
@@ -3489,28 +3489,28 @@
         <v>18.825</v>
       </c>
       <c r="M27">
-        <v>2.0223</v>
+        <v>2.103192</v>
       </c>
       <c r="N27">
-        <v>16.8027</v>
+        <v>16.721808</v>
       </c>
       <c r="O27">
-        <v>4.032647999999999</v>
+        <v>4.013233919999999</v>
       </c>
       <c r="P27">
-        <v>12.770052</v>
+        <v>12.70857408</v>
       </c>
       <c r="Q27">
-        <v>20.570052</v>
+        <v>20.50857408</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1594407316790362</v>
+        <v>0.1606823497939883</v>
       </c>
       <c r="T27">
-        <v>0.5583592101343421</v>
+        <v>0.5644597420449531</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.308707906838746</v>
+        <v>8.950680679652642</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1294765388475514</v>
+        <v>0.1292075289358256</v>
       </c>
       <c r="C28">
-        <v>150.8460726700603</v>
+        <v>149.9307372138176</v>
       </c>
       <c r="D28">
-        <v>184.9980726700603</v>
+        <v>185.5947372138176</v>
       </c>
       <c r="E28">
-        <v>2.012</v>
+        <v>3.524000000000001</v>
       </c>
       <c r="F28">
-        <v>39.312</v>
+        <v>40.824</v>
       </c>
       <c r="G28">
         <v>5.16</v>
@@ -3571,28 +3571,28 @@
         <v>18.825</v>
       </c>
       <c r="M28">
-        <v>2.103192</v>
+        <v>2.184084</v>
       </c>
       <c r="N28">
-        <v>16.721808</v>
+        <v>16.640916</v>
       </c>
       <c r="O28">
-        <v>4.013233919999999</v>
+        <v>3.99381984</v>
       </c>
       <c r="P28">
-        <v>12.70857408</v>
+        <v>12.64709616</v>
       </c>
       <c r="Q28">
-        <v>20.50857408</v>
+        <v>20.44709616</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1606823497939883</v>
+        <v>0.1619579848435967</v>
       </c>
       <c r="T28">
-        <v>0.5644597420449531</v>
+        <v>0.5707274118161287</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.950680679652642</v>
+        <v>8.619173987813657</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1292075289358256</v>
+        <v>0.1289385190240998</v>
       </c>
       <c r="C29">
-        <v>149.9307372138176</v>
+        <v>149.0192629924906</v>
       </c>
       <c r="D29">
-        <v>185.5947372138176</v>
+        <v>186.1952629924906</v>
       </c>
       <c r="E29">
-        <v>3.524000000000001</v>
+        <v>5.036000000000001</v>
       </c>
       <c r="F29">
-        <v>40.824</v>
+        <v>42.336</v>
       </c>
       <c r="G29">
         <v>5.16</v>
@@ -3653,28 +3653,28 @@
         <v>18.825</v>
       </c>
       <c r="M29">
-        <v>2.184084</v>
+        <v>2.264976</v>
       </c>
       <c r="N29">
-        <v>16.640916</v>
+        <v>16.560024</v>
       </c>
       <c r="O29">
-        <v>3.99381984</v>
+        <v>3.974405759999999</v>
       </c>
       <c r="P29">
-        <v>12.64709616</v>
+        <v>12.58561824</v>
       </c>
       <c r="Q29">
-        <v>20.44709616</v>
+        <v>20.38561824</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1619579848435967</v>
+        <v>0.1632690542001385</v>
       </c>
       <c r="T29">
-        <v>0.5707274118161287</v>
+        <v>0.5771691835253926</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.619173987813657</v>
+        <v>8.311346345391739</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1289385190240998</v>
+        <v>0.1286695091123739</v>
       </c>
       <c r="C30">
-        <v>149.0192629924906</v>
+        <v>148.1116876089494</v>
       </c>
       <c r="D30">
-        <v>186.1952629924906</v>
+        <v>186.7996876089493</v>
       </c>
       <c r="E30">
-        <v>5.036000000000001</v>
+        <v>6.548000000000002</v>
       </c>
       <c r="F30">
-        <v>42.336</v>
+        <v>43.848</v>
       </c>
       <c r="G30">
         <v>5.16</v>
@@ -3735,28 +3735,28 @@
         <v>18.825</v>
       </c>
       <c r="M30">
-        <v>2.264976</v>
+        <v>2.345868</v>
       </c>
       <c r="N30">
-        <v>16.560024</v>
+        <v>16.479132</v>
       </c>
       <c r="O30">
-        <v>3.974405759999999</v>
+        <v>3.95499168</v>
       </c>
       <c r="P30">
-        <v>12.58561824</v>
+        <v>12.52414032</v>
       </c>
       <c r="Q30">
-        <v>20.38561824</v>
+        <v>20.32414032</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1632690542001385</v>
+        <v>0.1646170550878506</v>
       </c>
       <c r="T30">
-        <v>0.5771691835253926</v>
+        <v>0.583792413592664</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.311346345391739</v>
+        <v>8.024748195550645</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1286695091123739</v>
+        <v>0.1284004992006481</v>
       </c>
       <c r="C31">
-        <v>148.1116876089494</v>
+        <v>147.2080491559181</v>
       </c>
       <c r="D31">
-        <v>186.7996876089493</v>
+        <v>187.4080491559181</v>
       </c>
       <c r="E31">
-        <v>6.547999999999995</v>
+        <v>8.059999999999995</v>
       </c>
       <c r="F31">
-        <v>43.84799999999999</v>
+        <v>45.35999999999999</v>
       </c>
       <c r="G31">
         <v>5.16</v>
@@ -3817,28 +3817,28 @@
         <v>18.825</v>
       </c>
       <c r="M31">
-        <v>2.345867999999999</v>
+        <v>2.426759999999999</v>
       </c>
       <c r="N31">
-        <v>16.479132</v>
+        <v>16.39824</v>
       </c>
       <c r="O31">
-        <v>3.95499168</v>
+        <v>3.9355776</v>
       </c>
       <c r="P31">
-        <v>12.52414032</v>
+        <v>12.4626624</v>
       </c>
       <c r="Q31">
-        <v>20.32414032</v>
+        <v>20.2626624</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1646170550878506</v>
+        <v>0.1660035702866401</v>
       </c>
       <c r="T31">
-        <v>0.583792413592664</v>
+        <v>0.5906048788047144</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.024748195550647</v>
+        <v>7.757256589032292</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1284004992006481</v>
+        <v>0.1283199692889223</v>
       </c>
       <c r="C32">
-        <v>147.2080491559181</v>
+        <v>145.8789376589711</v>
       </c>
       <c r="D32">
-        <v>187.4080491559181</v>
+        <v>187.5909376589711</v>
       </c>
       <c r="E32">
-        <v>8.059999999999995</v>
+        <v>9.571999999999996</v>
       </c>
       <c r="F32">
-        <v>45.35999999999999</v>
+        <v>46.87199999999999</v>
       </c>
       <c r="G32">
         <v>5.16</v>
@@ -3899,45 +3899,45 @@
         <v>18.825</v>
       </c>
       <c r="M32">
-        <v>2.426759999999999</v>
+        <v>2.5451496</v>
       </c>
       <c r="N32">
-        <v>16.39824</v>
+        <v>16.2798504</v>
       </c>
       <c r="O32">
-        <v>3.9355776</v>
+        <v>3.907164096</v>
       </c>
       <c r="P32">
-        <v>12.4626624</v>
+        <v>12.372686304</v>
       </c>
       <c r="Q32">
-        <v>20.2626624</v>
+        <v>20.172686304</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1660035702866401</v>
+        <v>0.1674302743317715</v>
       </c>
       <c r="T32">
-        <v>0.5906048788047144</v>
+        <v>0.5976148067765344</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.757256589032292</v>
+        <v>7.396421805618028</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1283199692889223</v>
+        <v>0.1280570393771965</v>
       </c>
       <c r="C33">
-        <v>145.8789376589711</v>
+        <v>144.9665613392382</v>
       </c>
       <c r="D33">
-        <v>187.5909376589711</v>
+        <v>188.1905613392383</v>
       </c>
       <c r="E33">
-        <v>9.571999999999996</v>
+        <v>11.084</v>
       </c>
       <c r="F33">
-        <v>46.87199999999999</v>
+        <v>48.384</v>
       </c>
       <c r="G33">
         <v>5.16</v>
@@ -3981,28 +3981,28 @@
         <v>18.825</v>
       </c>
       <c r="M33">
-        <v>2.5451496</v>
+        <v>2.6272512</v>
       </c>
       <c r="N33">
-        <v>16.2798504</v>
+        <v>16.1977488</v>
       </c>
       <c r="O33">
-        <v>3.907164096</v>
+        <v>3.887459712</v>
       </c>
       <c r="P33">
-        <v>12.372686304</v>
+        <v>12.310289088</v>
       </c>
       <c r="Q33">
-        <v>20.172686304</v>
+        <v>20.110289088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1674302743317715</v>
+        <v>0.1688989402605831</v>
       </c>
       <c r="T33">
-        <v>0.5976148067765344</v>
+        <v>0.6048309091004669</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.396421805618028</v>
+        <v>7.165283624192464</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1280570393771965</v>
+        <v>0.1277941094654707</v>
       </c>
       <c r="C34">
-        <v>144.9665613392382</v>
+        <v>144.058030637254</v>
       </c>
       <c r="D34">
-        <v>188.1905613392383</v>
+        <v>188.794030637254</v>
       </c>
       <c r="E34">
-        <v>11.084</v>
+        <v>12.596</v>
       </c>
       <c r="F34">
-        <v>48.384</v>
+        <v>49.896</v>
       </c>
       <c r="G34">
         <v>5.16</v>
@@ -4063,28 +4063,28 @@
         <v>18.825</v>
       </c>
       <c r="M34">
-        <v>2.6272512</v>
+        <v>2.7093528</v>
       </c>
       <c r="N34">
-        <v>16.1977488</v>
+        <v>16.1156472</v>
       </c>
       <c r="O34">
-        <v>3.887459712</v>
+        <v>3.867755327999999</v>
       </c>
       <c r="P34">
-        <v>12.310289088</v>
+        <v>12.247891872</v>
       </c>
       <c r="Q34">
-        <v>20.110289088</v>
+        <v>20.047891872</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1688989402605831</v>
+        <v>0.1704114469633891</v>
       </c>
       <c r="T34">
-        <v>0.6048309091004669</v>
+        <v>0.6122624174639197</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.165283624192464</v>
+        <v>6.948153817398752</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1277941094654707</v>
+        <v>0.1275311795537449</v>
       </c>
       <c r="C35">
-        <v>144.058030637254</v>
+        <v>143.1533826671752</v>
       </c>
       <c r="D35">
-        <v>188.794030637254</v>
+        <v>189.4013826671752</v>
       </c>
       <c r="E35">
-        <v>12.596</v>
+        <v>14.108</v>
       </c>
       <c r="F35">
-        <v>49.896</v>
+        <v>51.408</v>
       </c>
       <c r="G35">
         <v>5.16</v>
@@ -4145,28 +4145,28 @@
         <v>18.825</v>
       </c>
       <c r="M35">
-        <v>2.7093528</v>
+        <v>2.7914544</v>
       </c>
       <c r="N35">
-        <v>16.1156472</v>
+        <v>16.0335456</v>
       </c>
       <c r="O35">
-        <v>3.867755327999999</v>
+        <v>3.848050944</v>
       </c>
       <c r="P35">
-        <v>12.247891872</v>
+        <v>12.185494656</v>
       </c>
       <c r="Q35">
-        <v>20.047891872</v>
+        <v>19.985494656</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1704114469633891</v>
+        <v>0.1719697872026437</v>
       </c>
       <c r="T35">
-        <v>0.6122624174639197</v>
+        <v>0.6199191230505074</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.948153817398752</v>
+        <v>6.743796352181143</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1275311795537449</v>
+        <v>0.127268249642019</v>
       </c>
       <c r="C36">
-        <v>143.1533826671752</v>
+        <v>142.252655022286</v>
       </c>
       <c r="D36">
-        <v>189.4013826671752</v>
+        <v>190.012655022286</v>
       </c>
       <c r="E36">
-        <v>14.108</v>
+        <v>15.62</v>
       </c>
       <c r="F36">
-        <v>51.408</v>
+        <v>52.92</v>
       </c>
       <c r="G36">
         <v>5.16</v>
@@ -4227,28 +4227,28 @@
         <v>18.825</v>
       </c>
       <c r="M36">
-        <v>2.7914544</v>
+        <v>2.873556</v>
       </c>
       <c r="N36">
-        <v>16.0335456</v>
+        <v>15.951444</v>
       </c>
       <c r="O36">
-        <v>3.848050944</v>
+        <v>3.82834656</v>
       </c>
       <c r="P36">
-        <v>12.185494656</v>
+        <v>12.12309744</v>
       </c>
       <c r="Q36">
-        <v>19.985494656</v>
+        <v>19.92309744</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1719697872026437</v>
+        <v>0.173576076372337</v>
       </c>
       <c r="T36">
-        <v>0.6199191230505074</v>
+        <v>0.627811419578221</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.743796352181143</v>
+        <v>6.551116456404538</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.127268249642019</v>
+        <v>0.1270053197302932</v>
       </c>
       <c r="C37">
-        <v>142.252655022286</v>
+        <v>141.3558857827549</v>
       </c>
       <c r="D37">
-        <v>190.012655022286</v>
+        <v>190.6278857827549</v>
       </c>
       <c r="E37">
-        <v>15.62</v>
+        <v>17.13200000000001</v>
       </c>
       <c r="F37">
-        <v>52.92</v>
+        <v>54.432</v>
       </c>
       <c r="G37">
         <v>5.16</v>
@@ -4309,28 +4309,28 @@
         <v>18.825</v>
       </c>
       <c r="M37">
-        <v>2.873556</v>
+        <v>2.9556576</v>
       </c>
       <c r="N37">
-        <v>15.951444</v>
+        <v>15.8693424</v>
       </c>
       <c r="O37">
-        <v>3.82834656</v>
+        <v>3.808642176</v>
       </c>
       <c r="P37">
-        <v>12.12309744</v>
+        <v>12.060700224</v>
       </c>
       <c r="Q37">
-        <v>19.92309744</v>
+        <v>19.860700224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.173576076372337</v>
+        <v>0.1752325620785832</v>
       </c>
       <c r="T37">
-        <v>0.627811419578221</v>
+        <v>0.6359503503724256</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.551116456404538</v>
+        <v>6.369140999282189</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1270053197302932</v>
+        <v>0.1267423898185674</v>
       </c>
       <c r="C38">
-        <v>141.3558857827549</v>
+        <v>140.463113523543</v>
       </c>
       <c r="D38">
-        <v>190.6278857827549</v>
+        <v>191.247113523543</v>
       </c>
       <c r="E38">
-        <v>17.132</v>
+        <v>18.644</v>
       </c>
       <c r="F38">
-        <v>54.432</v>
+        <v>55.944</v>
       </c>
       <c r="G38">
         <v>5.16</v>
@@ -4391,28 +4391,28 @@
         <v>18.825</v>
       </c>
       <c r="M38">
-        <v>2.9556576</v>
+        <v>3.0377592</v>
       </c>
       <c r="N38">
-        <v>15.8693424</v>
+        <v>15.7872408</v>
       </c>
       <c r="O38">
-        <v>3.808642176</v>
+        <v>3.788937792</v>
       </c>
       <c r="P38">
-        <v>12.060700224</v>
+        <v>11.998303008</v>
       </c>
       <c r="Q38">
-        <v>19.860700224</v>
+        <v>19.798303008</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1752325620785832</v>
+        <v>0.1769416346326467</v>
       </c>
       <c r="T38">
-        <v>0.6359503503724255</v>
+        <v>0.6443476599220016</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.36914099928219</v>
+        <v>6.197002053355645</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1267423898185674</v>
+        <v>0.1267682599068416</v>
       </c>
       <c r="C39">
-        <v>140.463113523543</v>
+        <v>138.8900083483208</v>
       </c>
       <c r="D39">
-        <v>191.247113523543</v>
+        <v>191.1860083483208</v>
       </c>
       <c r="E39">
-        <v>18.644</v>
+        <v>20.156</v>
       </c>
       <c r="F39">
-        <v>55.944</v>
+        <v>57.456</v>
       </c>
       <c r="G39">
         <v>5.16</v>
@@ -4473,45 +4473,45 @@
         <v>18.825</v>
       </c>
       <c r="M39">
-        <v>3.0377592</v>
+        <v>3.1773168</v>
       </c>
       <c r="N39">
-        <v>15.7872408</v>
+        <v>15.6476832</v>
       </c>
       <c r="O39">
-        <v>3.788937792</v>
+        <v>3.755443968</v>
       </c>
       <c r="P39">
-        <v>11.998303008</v>
+        <v>11.892239232</v>
       </c>
       <c r="Q39">
-        <v>19.798303008</v>
+        <v>19.692239232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1769416346326467</v>
+        <v>0.178705838559422</v>
       </c>
       <c r="T39">
-        <v>0.6443476599220016</v>
+        <v>0.6530158504247899</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.197002053355645</v>
+        <v>5.92481051936653</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1267682599068416</v>
+        <v>0.1265129299951158</v>
       </c>
       <c r="C40">
-        <v>138.8900083483208</v>
+        <v>137.9828123944351</v>
       </c>
       <c r="D40">
-        <v>191.1860083483208</v>
+        <v>191.7908123944351</v>
       </c>
       <c r="E40">
-        <v>20.156</v>
+        <v>21.668</v>
       </c>
       <c r="F40">
-        <v>57.456</v>
+        <v>58.968</v>
       </c>
       <c r="G40">
         <v>5.16</v>
@@ -4555,28 +4555,28 @@
         <v>18.825</v>
       </c>
       <c r="M40">
-        <v>3.1773168</v>
+        <v>3.2609304</v>
       </c>
       <c r="N40">
-        <v>15.6476832</v>
+        <v>15.5640696</v>
       </c>
       <c r="O40">
-        <v>3.755443968</v>
+        <v>3.735376704</v>
       </c>
       <c r="P40">
-        <v>11.892239232</v>
+        <v>11.828692896</v>
       </c>
       <c r="Q40">
-        <v>19.692239232</v>
+        <v>19.628692896</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.178705838559422</v>
+        <v>0.1805278852378948</v>
       </c>
       <c r="T40">
-        <v>0.6530158504247899</v>
+        <v>0.6619682438948827</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.92481051936653</v>
+        <v>5.772892300921234</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1265129299951158</v>
+        <v>0.12625760008339</v>
       </c>
       <c r="C41">
-        <v>137.9828123944351</v>
+        <v>137.0794550975203</v>
       </c>
       <c r="D41">
-        <v>191.7908123944351</v>
+        <v>192.3994550975202</v>
       </c>
       <c r="E41">
-        <v>21.668</v>
+        <v>23.18</v>
       </c>
       <c r="F41">
-        <v>58.968</v>
+        <v>60.48</v>
       </c>
       <c r="G41">
         <v>5.16</v>
@@ -4637,28 +4637,28 @@
         <v>18.825</v>
       </c>
       <c r="M41">
-        <v>3.2609304</v>
+        <v>3.344544</v>
       </c>
       <c r="N41">
-        <v>15.5640696</v>
+        <v>15.480456</v>
       </c>
       <c r="O41">
-        <v>3.735376704</v>
+        <v>3.71530944</v>
       </c>
       <c r="P41">
-        <v>11.828692896</v>
+        <v>11.76514656</v>
       </c>
       <c r="Q41">
-        <v>19.628692896</v>
+        <v>19.56514656</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1805278852378948</v>
+        <v>0.18241066680565</v>
       </c>
       <c r="T41">
-        <v>0.6619682438948827</v>
+        <v>0.6712190504806453</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.772892300921234</v>
+        <v>5.628569993398203</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.12625760008339</v>
+        <v>0.1260022701716642</v>
       </c>
       <c r="C42">
-        <v>137.0794550975203</v>
+        <v>136.1799731195289</v>
       </c>
       <c r="D42">
-        <v>192.3994550975202</v>
+        <v>193.0119731195289</v>
       </c>
       <c r="E42">
-        <v>23.18</v>
+        <v>24.692</v>
       </c>
       <c r="F42">
-        <v>60.48</v>
+        <v>61.992</v>
       </c>
       <c r="G42">
         <v>5.16</v>
@@ -4719,28 +4719,28 @@
         <v>18.825</v>
       </c>
       <c r="M42">
-        <v>3.344544</v>
+        <v>3.4281576</v>
       </c>
       <c r="N42">
-        <v>15.480456</v>
+        <v>15.3968424</v>
       </c>
       <c r="O42">
-        <v>3.71530944</v>
+        <v>3.695242175999999</v>
       </c>
       <c r="P42">
-        <v>11.76514656</v>
+        <v>11.701600224</v>
       </c>
       <c r="Q42">
-        <v>19.56514656</v>
+        <v>19.501600224</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.18241066680565</v>
+        <v>0.1843572714773969</v>
       </c>
       <c r="T42">
-        <v>0.6712190504806453</v>
+        <v>0.6807834437303319</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.628569993398203</v>
+        <v>5.491287798437271</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1260022701716642</v>
+        <v>0.1257469402599384</v>
       </c>
       <c r="C43">
-        <v>136.1799731195289</v>
+        <v>135.2844035907688</v>
       </c>
       <c r="D43">
-        <v>193.0119731195289</v>
+        <v>193.6284035907688</v>
       </c>
       <c r="E43">
-        <v>24.692</v>
+        <v>26.204</v>
       </c>
       <c r="F43">
-        <v>61.992</v>
+        <v>63.504</v>
       </c>
       <c r="G43">
         <v>5.16</v>
@@ -4801,28 +4801,28 @@
         <v>18.825</v>
       </c>
       <c r="M43">
-        <v>3.4281576</v>
+        <v>3.5117712</v>
       </c>
       <c r="N43">
-        <v>15.3968424</v>
+        <v>15.3132288</v>
       </c>
       <c r="O43">
-        <v>3.695242175999999</v>
+        <v>3.675174912</v>
       </c>
       <c r="P43">
-        <v>11.701600224</v>
+        <v>11.638053888</v>
       </c>
       <c r="Q43">
-        <v>19.501600224</v>
+        <v>19.438053888</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1843572714773969</v>
+        <v>0.1863710004481696</v>
       </c>
       <c r="T43">
-        <v>0.6807834437303319</v>
+        <v>0.690677643643801</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.491287798437271</v>
+        <v>5.360542850855431</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1257469402599384</v>
+        <v>0.1254916103482125</v>
       </c>
       <c r="C44">
-        <v>135.2844035907689</v>
+        <v>134.3927841174067</v>
       </c>
       <c r="D44">
-        <v>193.6284035907689</v>
+        <v>194.2487841174067</v>
       </c>
       <c r="E44">
-        <v>26.20399999999999</v>
+        <v>27.71599999999999</v>
       </c>
       <c r="F44">
-        <v>63.50399999999999</v>
+        <v>65.01599999999999</v>
       </c>
       <c r="G44">
         <v>5.16</v>
@@ -4883,28 +4883,28 @@
         <v>18.825</v>
       </c>
       <c r="M44">
-        <v>3.5117712</v>
+        <v>3.5953848</v>
       </c>
       <c r="N44">
-        <v>15.3132288</v>
+        <v>15.2296152</v>
       </c>
       <c r="O44">
-        <v>3.675174912</v>
+        <v>3.655107648</v>
       </c>
       <c r="P44">
-        <v>11.638053888</v>
+        <v>11.574507552</v>
       </c>
       <c r="Q44">
-        <v>19.438053888</v>
+        <v>19.374507552</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1863710004481696</v>
+        <v>0.1884553865758115</v>
       </c>
       <c r="T44">
-        <v>0.6906776436438009</v>
+        <v>0.7009190084665144</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.360542850855432</v>
+        <v>5.235879063626236</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1254916103482125</v>
+        <v>0.1252362804364867</v>
       </c>
       <c r="C45">
-        <v>134.3927841174067</v>
+        <v>133.5051527891146</v>
       </c>
       <c r="D45">
-        <v>194.2487841174067</v>
+        <v>194.8731527891146</v>
       </c>
       <c r="E45">
-        <v>27.71599999999999</v>
+        <v>29.22799999999999</v>
       </c>
       <c r="F45">
-        <v>65.01599999999999</v>
+        <v>66.52799999999999</v>
       </c>
       <c r="G45">
         <v>5.16</v>
@@ -4965,28 +4965,28 @@
         <v>18.825</v>
       </c>
       <c r="M45">
-        <v>3.5953848</v>
+        <v>3.6789984</v>
       </c>
       <c r="N45">
-        <v>15.2296152</v>
+        <v>15.1460016</v>
       </c>
       <c r="O45">
-        <v>3.655107648</v>
+        <v>3.635040384</v>
       </c>
       <c r="P45">
-        <v>11.574507552</v>
+        <v>11.510961216</v>
       </c>
       <c r="Q45">
-        <v>19.374507552</v>
+        <v>19.310961216</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1884553865758115</v>
+        <v>0.1906142150651549</v>
       </c>
       <c r="T45">
-        <v>0.7009190084665144</v>
+        <v>0.7115261363186106</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.235879063626236</v>
+        <v>5.116881812180185</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1252362804364867</v>
+        <v>0.1249809505247609</v>
       </c>
       <c r="C46">
-        <v>133.5051527891146</v>
+        <v>132.6215481868664</v>
       </c>
       <c r="D46">
-        <v>194.8731527891146</v>
+        <v>195.5015481868664</v>
       </c>
       <c r="E46">
-        <v>29.22799999999999</v>
+        <v>30.73999999999999</v>
       </c>
       <c r="F46">
-        <v>66.52799999999999</v>
+        <v>68.03999999999999</v>
       </c>
       <c r="G46">
         <v>5.16</v>
@@ -5047,28 +5047,28 @@
         <v>18.825</v>
       </c>
       <c r="M46">
-        <v>3.6789984</v>
+        <v>3.762612</v>
       </c>
       <c r="N46">
-        <v>15.1460016</v>
+        <v>15.062388</v>
       </c>
       <c r="O46">
-        <v>3.635040384</v>
+        <v>3.61497312</v>
       </c>
       <c r="P46">
-        <v>11.510961216</v>
+        <v>11.44741488</v>
       </c>
       <c r="Q46">
-        <v>19.310961216</v>
+        <v>19.24741488</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1906142150651549</v>
+        <v>0.1928515464086562</v>
       </c>
       <c r="T46">
-        <v>0.7115261363186106</v>
+        <v>0.7225189779107831</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.116881812180185</v>
+        <v>5.00317332746507</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1249809505247609</v>
+        <v>0.1247256206130351</v>
       </c>
       <c r="C47">
-        <v>132.6215481868664</v>
+        <v>131.7420093908847</v>
       </c>
       <c r="D47">
-        <v>195.5015481868664</v>
+        <v>196.1340093908847</v>
       </c>
       <c r="E47">
-        <v>30.73999999999999</v>
+        <v>32.252</v>
       </c>
       <c r="F47">
-        <v>68.03999999999999</v>
+        <v>69.55199999999999</v>
       </c>
       <c r="G47">
         <v>5.16</v>
@@ -5129,28 +5129,28 @@
         <v>18.825</v>
       </c>
       <c r="M47">
-        <v>3.762612</v>
+        <v>3.8462256</v>
       </c>
       <c r="N47">
-        <v>15.062388</v>
+        <v>14.9787744</v>
       </c>
       <c r="O47">
-        <v>3.61497312</v>
+        <v>3.594905856</v>
       </c>
       <c r="P47">
-        <v>11.44741488</v>
+        <v>11.383868544</v>
       </c>
       <c r="Q47">
-        <v>19.24741488</v>
+        <v>19.183868544</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1928515464086562</v>
+        <v>0.1951717418759909</v>
       </c>
       <c r="T47">
-        <v>0.7225189779107831</v>
+        <v>0.7339189617841471</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.00317332746507</v>
+        <v>4.894408689911481</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1247256206130351</v>
+        <v>0.1244702907013093</v>
       </c>
       <c r="C48">
-        <v>131.7420093908847</v>
+        <v>130.8665759887423</v>
       </c>
       <c r="D48">
-        <v>196.1340093908847</v>
+        <v>196.7705759887423</v>
       </c>
       <c r="E48">
-        <v>32.252</v>
+        <v>33.764</v>
       </c>
       <c r="F48">
-        <v>69.55199999999999</v>
+        <v>71.06399999999999</v>
       </c>
       <c r="G48">
         <v>5.16</v>
@@ -5211,28 +5211,28 @@
         <v>18.825</v>
       </c>
       <c r="M48">
-        <v>3.8462256</v>
+        <v>3.9298392</v>
       </c>
       <c r="N48">
-        <v>14.9787744</v>
+        <v>14.8951608</v>
       </c>
       <c r="O48">
-        <v>3.594905856</v>
+        <v>3.574838592</v>
       </c>
       <c r="P48">
-        <v>11.383868544</v>
+        <v>11.320322208</v>
       </c>
       <c r="Q48">
-        <v>19.183868544</v>
+        <v>19.120322208</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1951717418759909</v>
+        <v>0.1975794918892628</v>
       </c>
       <c r="T48">
-        <v>0.7339189617841471</v>
+        <v>0.745749133728204</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.894408689911481</v>
+        <v>4.790272334806982</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1244702907013093</v>
+        <v>0.1242149607895835</v>
       </c>
       <c r="C49">
-        <v>130.8665759887423</v>
+        <v>129.9952880836226</v>
       </c>
       <c r="D49">
-        <v>196.7705759887423</v>
+        <v>197.4112880836226</v>
       </c>
       <c r="E49">
-        <v>33.764</v>
+        <v>35.276</v>
       </c>
       <c r="F49">
-        <v>71.06399999999999</v>
+        <v>72.57599999999999</v>
       </c>
       <c r="G49">
         <v>5.16</v>
@@ -5293,28 +5293,28 @@
         <v>18.825</v>
       </c>
       <c r="M49">
-        <v>3.9298392</v>
+        <v>4.0134528</v>
       </c>
       <c r="N49">
-        <v>14.8951608</v>
+        <v>14.8115472</v>
       </c>
       <c r="O49">
-        <v>3.574838592</v>
+        <v>3.554771328</v>
       </c>
       <c r="P49">
-        <v>11.320322208</v>
+        <v>11.256775872</v>
       </c>
       <c r="Q49">
-        <v>19.120322208</v>
+        <v>19.056775872</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1975794918892628</v>
+        <v>0.2000798476722759</v>
       </c>
       <c r="T49">
-        <v>0.745749133728204</v>
+        <v>0.7580343122854938</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.790272334806982</v>
+        <v>4.690474994498503</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1242149607895835</v>
+        <v>0.1239596308778576</v>
       </c>
       <c r="C50">
-        <v>129.9952880836226</v>
+        <v>129.1281863027409</v>
       </c>
       <c r="D50">
-        <v>197.4112880836226</v>
+        <v>198.0561863027409</v>
       </c>
       <c r="E50">
-        <v>35.276</v>
+        <v>36.788</v>
       </c>
       <c r="F50">
-        <v>72.57599999999999</v>
+        <v>74.08799999999999</v>
       </c>
       <c r="G50">
         <v>5.16</v>
@@ -5375,28 +5375,28 @@
         <v>18.825</v>
       </c>
       <c r="M50">
-        <v>4.0134528</v>
+        <v>4.0970664</v>
       </c>
       <c r="N50">
-        <v>14.8115472</v>
+        <v>14.7279336</v>
       </c>
       <c r="O50">
-        <v>3.554771328</v>
+        <v>3.534704064</v>
       </c>
       <c r="P50">
-        <v>11.256775872</v>
+        <v>11.193229536</v>
       </c>
       <c r="Q50">
-        <v>19.056775872</v>
+        <v>18.993229536</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2000798476722759</v>
+        <v>0.2026782566232503</v>
       </c>
       <c r="T50">
-        <v>0.7580343122854938</v>
+        <v>0.7708012625509126</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.690474994498503</v>
+        <v>4.594751015018941</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1239596308778576</v>
+        <v>0.1237043009661318</v>
       </c>
       <c r="C51">
-        <v>129.1281863027409</v>
+        <v>128.2653118059324</v>
       </c>
       <c r="D51">
-        <v>198.0561863027409</v>
+        <v>198.7053118059324</v>
       </c>
       <c r="E51">
-        <v>36.788</v>
+        <v>38.3</v>
       </c>
       <c r="F51">
-        <v>74.08799999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G51">
         <v>5.16</v>
@@ -5457,28 +5457,28 @@
         <v>18.825</v>
       </c>
       <c r="M51">
-        <v>4.0970664</v>
+        <v>4.18068</v>
       </c>
       <c r="N51">
-        <v>14.7279336</v>
+        <v>14.64432</v>
       </c>
       <c r="O51">
-        <v>3.534704064</v>
+        <v>3.5146368</v>
       </c>
       <c r="P51">
-        <v>11.193229536</v>
+        <v>11.1296832</v>
       </c>
       <c r="Q51">
-        <v>18.993229536</v>
+        <v>18.9296832</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2026782566232503</v>
+        <v>0.2053806019322637</v>
       </c>
       <c r="T51">
-        <v>0.7708012625509126</v>
+        <v>0.7840788908269485</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.594751015018941</v>
+        <v>4.502855994718563</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1237043009661318</v>
+        <v>0.124417971054406</v>
       </c>
       <c r="C52">
-        <v>128.2653118059324</v>
+        <v>124.9495252732203</v>
       </c>
       <c r="D52">
-        <v>198.7053118059324</v>
+        <v>196.9015252732203</v>
       </c>
       <c r="E52">
-        <v>38.3</v>
+        <v>39.812</v>
       </c>
       <c r="F52">
-        <v>75.59999999999999</v>
+        <v>77.11199999999999</v>
       </c>
       <c r="G52">
         <v>5.16</v>
@@ -5539,45 +5539,45 @@
         <v>18.825</v>
       </c>
       <c r="M52">
-        <v>4.18068</v>
+        <v>4.4570736</v>
       </c>
       <c r="N52">
-        <v>14.64432</v>
+        <v>14.3679264</v>
       </c>
       <c r="O52">
-        <v>3.5146368</v>
+        <v>3.448302335999999</v>
       </c>
       <c r="P52">
-        <v>11.1296832</v>
+        <v>10.919624064</v>
       </c>
       <c r="Q52">
-        <v>18.9296832</v>
+        <v>18.719624064</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2053806019322637</v>
+        <v>0.2081932470498082</v>
       </c>
       <c r="T52">
-        <v>0.7840788908269485</v>
+        <v>0.7978984631142509</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.24</v>
       </c>
       <c r="W52">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.502855994718563</v>
+        <v>4.223623320916216</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.124417971054406</v>
+        <v>0.1241816411426802</v>
       </c>
       <c r="C53">
-        <v>124.9495252732203</v>
+        <v>124.0312066430935</v>
       </c>
       <c r="D53">
-        <v>196.9015252732203</v>
+        <v>197.4952066430935</v>
       </c>
       <c r="E53">
-        <v>39.812</v>
+        <v>41.324</v>
       </c>
       <c r="F53">
-        <v>77.11199999999999</v>
+        <v>78.624</v>
       </c>
       <c r="G53">
         <v>5.16</v>
@@ -5621,28 +5621,28 @@
         <v>18.825</v>
       </c>
       <c r="M53">
-        <v>4.4570736</v>
+        <v>4.5444672</v>
       </c>
       <c r="N53">
-        <v>14.3679264</v>
+        <v>14.2805328</v>
       </c>
       <c r="O53">
-        <v>3.448302335999999</v>
+        <v>3.427327872</v>
       </c>
       <c r="P53">
-        <v>10.919624064</v>
+        <v>10.853204928</v>
       </c>
       <c r="Q53">
-        <v>18.719624064</v>
+        <v>18.653204928</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2081932470498082</v>
+        <v>0.2111230857139171</v>
       </c>
       <c r="T53">
-        <v>0.7978984631142509</v>
+        <v>0.8122938509135244</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.223623320916216</v>
+        <v>4.142399795513983</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1241816411426802</v>
+        <v>0.1239453112309544</v>
       </c>
       <c r="C54">
-        <v>124.0312066430935</v>
+        <v>123.1164788788428</v>
       </c>
       <c r="D54">
-        <v>197.4952066430935</v>
+        <v>198.0924788788428</v>
       </c>
       <c r="E54">
-        <v>41.324</v>
+        <v>42.836</v>
       </c>
       <c r="F54">
-        <v>78.624</v>
+        <v>80.136</v>
       </c>
       <c r="G54">
         <v>5.16</v>
@@ -5703,28 +5703,28 @@
         <v>18.825</v>
       </c>
       <c r="M54">
-        <v>4.5444672</v>
+        <v>4.6318608</v>
       </c>
       <c r="N54">
-        <v>14.2805328</v>
+        <v>14.1931392</v>
       </c>
       <c r="O54">
-        <v>3.427327872</v>
+        <v>3.406353408</v>
       </c>
       <c r="P54">
-        <v>10.853204928</v>
+        <v>10.786785792</v>
       </c>
       <c r="Q54">
-        <v>18.653204928</v>
+        <v>18.586785792</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2111230857139171</v>
+        <v>0.2141775983637328</v>
       </c>
       <c r="T54">
-        <v>0.8122938509135244</v>
+        <v>0.8273018084063838</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.142399795513983</v>
+        <v>4.064241308806171</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1239453112309544</v>
+        <v>0.1251453813192286</v>
       </c>
       <c r="C55">
-        <v>123.1164788788428</v>
+        <v>118.6084020478784</v>
       </c>
       <c r="D55">
-        <v>198.0924788788428</v>
+        <v>195.0964020478784</v>
       </c>
       <c r="E55">
-        <v>42.836</v>
+        <v>44.348</v>
       </c>
       <c r="F55">
-        <v>80.136</v>
+        <v>81.648</v>
       </c>
       <c r="G55">
         <v>5.16</v>
@@ -5785,45 +5785,45 @@
         <v>18.825</v>
       </c>
       <c r="M55">
-        <v>4.6318608</v>
+        <v>5.0050224</v>
       </c>
       <c r="N55">
-        <v>14.1931392</v>
+        <v>13.8199776</v>
       </c>
       <c r="O55">
-        <v>3.406353408</v>
+        <v>3.316794624</v>
       </c>
       <c r="P55">
-        <v>10.786785792</v>
+        <v>10.503182976</v>
       </c>
       <c r="Q55">
-        <v>18.586785792</v>
+        <v>18.303182976</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2141775983637328</v>
+        <v>0.2173649159113665</v>
       </c>
       <c r="T55">
-        <v>0.8273018084063838</v>
+        <v>0.842962285790237</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.064241308806171</v>
+        <v>3.761221927797965</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1251453813192286</v>
+        <v>0.1249356514075028</v>
       </c>
       <c r="C56">
-        <v>118.6084020478784</v>
+        <v>117.6134578937805</v>
       </c>
       <c r="D56">
-        <v>195.0964020478784</v>
+        <v>195.6134578937805</v>
       </c>
       <c r="E56">
-        <v>44.348</v>
+        <v>45.86</v>
       </c>
       <c r="F56">
-        <v>81.648</v>
+        <v>83.16</v>
       </c>
       <c r="G56">
         <v>5.16</v>
@@ -5867,28 +5867,28 @@
         <v>18.825</v>
       </c>
       <c r="M56">
-        <v>5.0050224</v>
+        <v>5.097708</v>
       </c>
       <c r="N56">
-        <v>13.8199776</v>
+        <v>13.727292</v>
       </c>
       <c r="O56">
-        <v>3.316794624</v>
+        <v>3.29455008</v>
       </c>
       <c r="P56">
-        <v>10.503182976</v>
+        <v>10.43274192</v>
       </c>
       <c r="Q56">
-        <v>18.303182976</v>
+        <v>18.23274192</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2173649159113665</v>
+        <v>0.2206938920166728</v>
       </c>
       <c r="T56">
-        <v>0.842962285790237</v>
+        <v>0.8593187843911506</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.761221927797965</v>
+        <v>3.692836074565275</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1249356514075028</v>
+        <v>0.1247259214957769</v>
       </c>
       <c r="C57">
-        <v>117.6134578937805</v>
+        <v>116.6212616854745</v>
       </c>
       <c r="D57">
-        <v>195.6134578937805</v>
+        <v>196.1332616854745</v>
       </c>
       <c r="E57">
-        <v>45.86</v>
+        <v>47.372</v>
       </c>
       <c r="F57">
-        <v>83.16</v>
+        <v>84.672</v>
       </c>
       <c r="G57">
         <v>5.16</v>
@@ -5949,28 +5949,28 @@
         <v>18.825</v>
       </c>
       <c r="M57">
-        <v>5.097708</v>
+        <v>5.1903936</v>
       </c>
       <c r="N57">
-        <v>13.727292</v>
+        <v>13.6346064</v>
       </c>
       <c r="O57">
-        <v>3.29455008</v>
+        <v>3.272305536</v>
       </c>
       <c r="P57">
-        <v>10.43274192</v>
+        <v>10.362300864</v>
       </c>
       <c r="Q57">
-        <v>18.23274192</v>
+        <v>18.162300864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2206938920166728</v>
+        <v>0.2241741852176749</v>
       </c>
       <c r="T57">
-        <v>0.8593187843911506</v>
+        <v>0.8764187602011965</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.692836074565275</v>
+        <v>3.626892573233752</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1247259214957769</v>
+        <v>0.1245161915840511</v>
       </c>
       <c r="C58">
-        <v>116.6212616854745</v>
+        <v>115.6318353876824</v>
       </c>
       <c r="D58">
-        <v>196.1332616854745</v>
+        <v>196.6558353876824</v>
       </c>
       <c r="E58">
-        <v>47.372</v>
+        <v>48.884</v>
       </c>
       <c r="F58">
-        <v>84.672</v>
+        <v>86.184</v>
       </c>
       <c r="G58">
         <v>5.16</v>
@@ -6031,28 +6031,28 @@
         <v>18.825</v>
       </c>
       <c r="M58">
-        <v>5.1903936</v>
+        <v>5.2830792</v>
       </c>
       <c r="N58">
-        <v>13.6346064</v>
+        <v>13.5419208</v>
       </c>
       <c r="O58">
-        <v>3.272305536</v>
+        <v>3.250060992</v>
       </c>
       <c r="P58">
-        <v>10.362300864</v>
+        <v>10.291859808</v>
       </c>
       <c r="Q58">
-        <v>18.162300864</v>
+        <v>18.091859808</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2241741852176749</v>
+        <v>0.2278163525210492</v>
       </c>
       <c r="T58">
-        <v>0.8764187602011965</v>
+        <v>0.8943140837233378</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.626892573233752</v>
+        <v>3.563262878966494</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1245161915840511</v>
+        <v>0.1243064616723253</v>
       </c>
       <c r="C59">
-        <v>115.6318353876824</v>
+        <v>114.6452011998416</v>
       </c>
       <c r="D59">
-        <v>196.6558353876824</v>
+        <v>197.1812011998416</v>
       </c>
       <c r="E59">
-        <v>48.884</v>
+        <v>50.396</v>
       </c>
       <c r="F59">
-        <v>86.184</v>
+        <v>87.696</v>
       </c>
       <c r="G59">
         <v>5.16</v>
@@ -6113,28 +6113,28 @@
         <v>18.825</v>
       </c>
       <c r="M59">
-        <v>5.2830792</v>
+        <v>5.3757648</v>
       </c>
       <c r="N59">
-        <v>13.5419208</v>
+        <v>13.4492352</v>
       </c>
       <c r="O59">
-        <v>3.250060992</v>
+        <v>3.227816448</v>
       </c>
       <c r="P59">
-        <v>10.291859808</v>
+        <v>10.221418752</v>
       </c>
       <c r="Q59">
-        <v>18.091859808</v>
+        <v>18.021418752</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2278163525210492</v>
+        <v>0.2316319563626793</v>
       </c>
       <c r="T59">
-        <v>0.8943140837233378</v>
+        <v>0.9130615655084378</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.563262878966494</v>
+        <v>3.501827312087761</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1243064616723253</v>
+        <v>0.1253522517605995</v>
       </c>
       <c r="C60">
-        <v>114.6452011998416</v>
+        <v>110.5410665808323</v>
       </c>
       <c r="D60">
-        <v>197.1812011998416</v>
+        <v>194.5890665808323</v>
       </c>
       <c r="E60">
-        <v>50.39599999999999</v>
+        <v>51.90799999999999</v>
       </c>
       <c r="F60">
-        <v>87.69599999999998</v>
+        <v>89.20799999999998</v>
       </c>
       <c r="G60">
         <v>5.16</v>
@@ -6195,45 +6195,45 @@
         <v>18.825</v>
       </c>
       <c r="M60">
-        <v>5.375764799999999</v>
+        <v>5.718232799999999</v>
       </c>
       <c r="N60">
-        <v>13.4492352</v>
+        <v>13.1067672</v>
       </c>
       <c r="O60">
-        <v>3.227816448</v>
+        <v>3.145624128</v>
       </c>
       <c r="P60">
-        <v>10.221418752</v>
+        <v>9.961143072</v>
       </c>
       <c r="Q60">
-        <v>18.021418752</v>
+        <v>17.761143072</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2316319563626793</v>
+        <v>0.2356336872209744</v>
       </c>
       <c r="T60">
-        <v>0.9130615655084378</v>
+        <v>0.9327235586001283</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.501827312087761</v>
+        <v>3.292101014145489</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1253522517605995</v>
+        <v>0.1251638018488737</v>
       </c>
       <c r="C61">
-        <v>110.5410665808323</v>
+        <v>109.4911197028564</v>
       </c>
       <c r="D61">
-        <v>194.5890665808323</v>
+        <v>195.0511197028563</v>
       </c>
       <c r="E61">
-        <v>51.90799999999999</v>
+        <v>53.41999999999999</v>
       </c>
       <c r="F61">
-        <v>89.20799999999998</v>
+        <v>90.71999999999998</v>
       </c>
       <c r="G61">
         <v>5.16</v>
@@ -6277,28 +6277,28 @@
         <v>18.825</v>
       </c>
       <c r="M61">
-        <v>5.718232799999999</v>
+        <v>5.815151999999999</v>
       </c>
       <c r="N61">
-        <v>13.1067672</v>
+        <v>13.009848</v>
       </c>
       <c r="O61">
-        <v>3.145624128</v>
+        <v>3.12236352</v>
       </c>
       <c r="P61">
-        <v>9.961143072</v>
+        <v>9.887484479999999</v>
       </c>
       <c r="Q61">
-        <v>17.761143072</v>
+        <v>17.68748448</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2356336872209744</v>
+        <v>0.2398355046221842</v>
       </c>
       <c r="T61">
-        <v>0.9327235586001283</v>
+        <v>0.953368651346403</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.292101014145489</v>
+        <v>3.237232663909731</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1251638018488737</v>
+        <v>0.1249753519371479</v>
       </c>
       <c r="C62">
-        <v>109.4911197028564</v>
+        <v>108.4433723445017</v>
       </c>
       <c r="D62">
-        <v>195.0511197028563</v>
+        <v>195.5153723445017</v>
       </c>
       <c r="E62">
-        <v>53.41999999999999</v>
+        <v>54.93199999999999</v>
       </c>
       <c r="F62">
-        <v>90.71999999999998</v>
+        <v>92.23199999999999</v>
       </c>
       <c r="G62">
         <v>5.16</v>
@@ -6359,28 +6359,28 @@
         <v>18.825</v>
       </c>
       <c r="M62">
-        <v>5.815151999999999</v>
+        <v>5.9120712</v>
       </c>
       <c r="N62">
-        <v>13.009848</v>
+        <v>12.9129288</v>
       </c>
       <c r="O62">
-        <v>3.12236352</v>
+        <v>3.099102912</v>
       </c>
       <c r="P62">
-        <v>9.887484479999999</v>
+        <v>9.813825888</v>
       </c>
       <c r="Q62">
-        <v>17.68748448</v>
+        <v>17.613825888</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2398355046221842</v>
+        <v>0.2442527998388407</v>
       </c>
       <c r="T62">
-        <v>0.953368651346403</v>
+        <v>0.9750724667976154</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.237232663909731</v>
+        <v>3.184163275976784</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1249753519371479</v>
+        <v>0.1247869020254221</v>
       </c>
       <c r="C63">
-        <v>108.4433723445017</v>
+        <v>107.3978402488575</v>
       </c>
       <c r="D63">
-        <v>195.5153723445017</v>
+        <v>195.9818402488575</v>
       </c>
       <c r="E63">
-        <v>54.93199999999999</v>
+        <v>56.44399999999999</v>
       </c>
       <c r="F63">
-        <v>92.23199999999999</v>
+        <v>93.74399999999999</v>
       </c>
       <c r="G63">
         <v>5.16</v>
@@ -6441,28 +6441,28 @@
         <v>18.825</v>
       </c>
       <c r="M63">
-        <v>5.9120712</v>
+        <v>6.008990399999999</v>
       </c>
       <c r="N63">
-        <v>12.9129288</v>
+        <v>12.8160096</v>
       </c>
       <c r="O63">
-        <v>3.099102912</v>
+        <v>3.075842304</v>
       </c>
       <c r="P63">
-        <v>9.813825888</v>
+        <v>9.740167296000001</v>
       </c>
       <c r="Q63">
-        <v>17.613825888</v>
+        <v>17.540167296</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2442527998388407</v>
+        <v>0.2489025842774265</v>
       </c>
       <c r="T63">
-        <v>0.9750724667976154</v>
+        <v>0.9979185883252072</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.184163275976784</v>
+        <v>3.132805803783611</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1247869020254221</v>
+        <v>0.1245984521136962</v>
       </c>
       <c r="C64">
-        <v>107.3978402488575</v>
+        <v>106.3545393096142</v>
       </c>
       <c r="D64">
-        <v>195.9818402488575</v>
+        <v>196.4505393096142</v>
       </c>
       <c r="E64">
-        <v>56.44399999999999</v>
+        <v>57.956</v>
       </c>
       <c r="F64">
-        <v>93.74399999999999</v>
+        <v>95.256</v>
       </c>
       <c r="G64">
         <v>5.16</v>
@@ -6523,28 +6523,28 @@
         <v>18.825</v>
       </c>
       <c r="M64">
-        <v>6.008990399999999</v>
+        <v>6.1059096</v>
       </c>
       <c r="N64">
-        <v>12.8160096</v>
+        <v>12.7190904</v>
       </c>
       <c r="O64">
-        <v>3.075842304</v>
+        <v>3.052581696</v>
       </c>
       <c r="P64">
-        <v>9.740167296000001</v>
+        <v>9.666508703999998</v>
       </c>
       <c r="Q64">
-        <v>17.540167296</v>
+        <v>17.466508704</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2489025842774265</v>
+        <v>0.2538037084153952</v>
       </c>
       <c r="T64">
-        <v>0.9979185883252072</v>
+        <v>1.021999635340777</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.132805803783611</v>
+        <v>3.083078727533077</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1245984521136962</v>
+        <v>0.1244100022019704</v>
       </c>
       <c r="C65">
-        <v>106.3545393096142</v>
+        <v>105.3134855728679</v>
       </c>
       <c r="D65">
-        <v>196.4505393096142</v>
+        <v>196.9214855728679</v>
       </c>
       <c r="E65">
-        <v>57.956</v>
+        <v>59.468</v>
       </c>
       <c r="F65">
-        <v>95.256</v>
+        <v>96.768</v>
       </c>
       <c r="G65">
         <v>5.16</v>
@@ -6605,28 +6605,28 @@
         <v>18.825</v>
       </c>
       <c r="M65">
-        <v>6.1059096</v>
+        <v>6.202828800000001</v>
       </c>
       <c r="N65">
-        <v>12.7190904</v>
+        <v>12.6221712</v>
       </c>
       <c r="O65">
-        <v>3.052581696</v>
+        <v>3.029321088</v>
       </c>
       <c r="P65">
-        <v>9.666508703999998</v>
+        <v>9.592850111999999</v>
       </c>
       <c r="Q65">
-        <v>17.466508704</v>
+        <v>17.392850112</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2538037084153952</v>
+        <v>0.2589771172276956</v>
       </c>
       <c r="T65">
-        <v>1.021999635340777</v>
+        <v>1.047418518301656</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.083078727533077</v>
+        <v>3.034905622415372</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1244100022019704</v>
+        <v>0.1280747522902446</v>
       </c>
       <c r="C66">
-        <v>105.3134855728679</v>
+        <v>95.03004583531154</v>
       </c>
       <c r="D66">
-        <v>196.9214855728679</v>
+        <v>188.1500458353115</v>
       </c>
       <c r="E66">
-        <v>59.468</v>
+        <v>60.98</v>
       </c>
       <c r="F66">
-        <v>96.768</v>
+        <v>98.28</v>
       </c>
       <c r="G66">
         <v>5.16</v>
@@ -6687,45 +6687,45 @@
         <v>18.825</v>
       </c>
       <c r="M66">
-        <v>6.202828800000001</v>
+        <v>7.066332000000001</v>
       </c>
       <c r="N66">
-        <v>12.6221712</v>
+        <v>11.758668</v>
       </c>
       <c r="O66">
-        <v>3.029321088</v>
+        <v>2.82208032</v>
       </c>
       <c r="P66">
-        <v>9.592850111999999</v>
+        <v>8.936587679999999</v>
       </c>
       <c r="Q66">
-        <v>17.392850112</v>
+        <v>16.73658768</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2589771172276956</v>
+        <v>0.264446149400699</v>
       </c>
       <c r="T66">
-        <v>1.047418518301656</v>
+        <v>1.0742899088603</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.034905622415372</v>
+        <v>2.664041259312469</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1280747522902446</v>
+        <v>0.1279455823785188</v>
       </c>
       <c r="C67">
-        <v>95.03004583531154</v>
+        <v>93.81390258266245</v>
       </c>
       <c r="D67">
-        <v>188.1500458353115</v>
+        <v>188.4459025826625</v>
       </c>
       <c r="E67">
-        <v>60.98</v>
+        <v>62.492</v>
       </c>
       <c r="F67">
-        <v>98.28</v>
+        <v>99.792</v>
       </c>
       <c r="G67">
         <v>5.16</v>
@@ -6769,28 +6769,28 @@
         <v>18.825</v>
       </c>
       <c r="M67">
-        <v>7.066332000000001</v>
+        <v>7.175044800000001</v>
       </c>
       <c r="N67">
-        <v>11.758668</v>
+        <v>11.6499552</v>
       </c>
       <c r="O67">
-        <v>2.82208032</v>
+        <v>2.795989247999999</v>
       </c>
       <c r="P67">
-        <v>8.936587679999999</v>
+        <v>8.853965951999998</v>
       </c>
       <c r="Q67">
-        <v>16.73658768</v>
+        <v>16.653965952</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.264446149400699</v>
+        <v>0.2702368893485848</v>
       </c>
       <c r="T67">
-        <v>1.0742899088603</v>
+        <v>1.102741969451805</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.664041259312469</v>
+        <v>2.623676997807734</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1279455823785188</v>
+        <v>0.127816412466793</v>
       </c>
       <c r="C68">
-        <v>93.81390258266245</v>
+        <v>92.59869123592804</v>
       </c>
       <c r="D68">
-        <v>188.4459025826625</v>
+        <v>188.742691235928</v>
       </c>
       <c r="E68">
-        <v>62.492</v>
+        <v>64.004</v>
       </c>
       <c r="F68">
-        <v>99.792</v>
+        <v>101.304</v>
       </c>
       <c r="G68">
         <v>5.16</v>
@@ -6851,28 +6851,28 @@
         <v>18.825</v>
       </c>
       <c r="M68">
-        <v>7.175044800000001</v>
+        <v>7.2837576</v>
       </c>
       <c r="N68">
-        <v>11.6499552</v>
+        <v>11.5412424</v>
       </c>
       <c r="O68">
-        <v>2.795989247999999</v>
+        <v>2.769898175999999</v>
       </c>
       <c r="P68">
-        <v>8.853965951999998</v>
+        <v>8.771344223999998</v>
       </c>
       <c r="Q68">
-        <v>16.653965952</v>
+        <v>16.571344224</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2702368893485848</v>
+        <v>0.2763785832327061</v>
       </c>
       <c r="T68">
-        <v>1.102741969451805</v>
+        <v>1.132918397351886</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.623676997807734</v>
+        <v>2.5845176396315</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.127816412466793</v>
+        <v>0.1276872425550672</v>
       </c>
       <c r="C69">
-        <v>92.59869123592804</v>
+        <v>91.38441620510676</v>
       </c>
       <c r="D69">
-        <v>188.742691235928</v>
+        <v>189.0404162051068</v>
       </c>
       <c r="E69">
-        <v>64.004</v>
+        <v>65.51600000000001</v>
       </c>
       <c r="F69">
-        <v>101.304</v>
+        <v>102.816</v>
       </c>
       <c r="G69">
         <v>5.16</v>
@@ -6933,28 +6933,28 @@
         <v>18.825</v>
       </c>
       <c r="M69">
-        <v>7.2837576</v>
+        <v>7.392470400000001</v>
       </c>
       <c r="N69">
-        <v>11.5412424</v>
+        <v>11.4325296</v>
       </c>
       <c r="O69">
-        <v>2.769898175999999</v>
+        <v>2.743807104</v>
       </c>
       <c r="P69">
-        <v>8.771344223999998</v>
+        <v>8.688722495999999</v>
       </c>
       <c r="Q69">
-        <v>16.571344224</v>
+        <v>16.488722496</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2763785832327061</v>
+        <v>0.282904132984585</v>
       </c>
       <c r="T69">
-        <v>1.132918397351886</v>
+        <v>1.164980851995722</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.5845176396315</v>
+        <v>2.546510027283978</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1276872425550672</v>
+        <v>0.1275580726433414</v>
       </c>
       <c r="C70">
-        <v>91.38441620510676</v>
+        <v>90.17108192806651</v>
       </c>
       <c r="D70">
-        <v>189.0404162051068</v>
+        <v>189.3390819280665</v>
       </c>
       <c r="E70">
-        <v>65.51600000000001</v>
+        <v>67.02800000000001</v>
       </c>
       <c r="F70">
-        <v>102.816</v>
+        <v>104.328</v>
       </c>
       <c r="G70">
         <v>5.16</v>
@@ -7015,28 +7015,28 @@
         <v>18.825</v>
       </c>
       <c r="M70">
-        <v>7.392470400000001</v>
+        <v>7.501183200000001</v>
       </c>
       <c r="N70">
-        <v>11.4325296</v>
+        <v>11.3238168</v>
       </c>
       <c r="O70">
-        <v>2.743807104</v>
+        <v>2.717716032</v>
       </c>
       <c r="P70">
-        <v>8.688722495999999</v>
+        <v>8.606100767999999</v>
       </c>
       <c r="Q70">
-        <v>16.488722496</v>
+        <v>16.406100768</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.282904132984585</v>
+        <v>0.2898506859462626</v>
       </c>
       <c r="T70">
-        <v>1.164980851995722</v>
+        <v>1.199111852100451</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.546510027283978</v>
+        <v>2.509604084859572</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1275580726433414</v>
+        <v>0.1295037027316156</v>
       </c>
       <c r="C71">
-        <v>90.17108192806651</v>
+        <v>84.25803630327943</v>
       </c>
       <c r="D71">
-        <v>189.3390819280665</v>
+        <v>184.9380363032794</v>
       </c>
       <c r="E71">
-        <v>67.02800000000001</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F71">
-        <v>104.328</v>
+        <v>105.84</v>
       </c>
       <c r="G71">
         <v>5.16</v>
@@ -7097,45 +7097,45 @@
         <v>18.825</v>
       </c>
       <c r="M71">
-        <v>7.501183200000001</v>
+        <v>8.022672000000002</v>
       </c>
       <c r="N71">
-        <v>11.3238168</v>
+        <v>10.802328</v>
       </c>
       <c r="O71">
-        <v>2.717716032</v>
+        <v>2.592558719999999</v>
       </c>
       <c r="P71">
-        <v>8.606100767999999</v>
+        <v>8.209769279999998</v>
       </c>
       <c r="Q71">
-        <v>16.406100768</v>
+        <v>16.00976928</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2898506859462626</v>
+        <v>0.2972603424387186</v>
       </c>
       <c r="T71">
-        <v>1.199111852100451</v>
+        <v>1.235518252212161</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.24</v>
       </c>
       <c r="W71">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.509604084859572</v>
+        <v>2.346475089596084</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1295037027316156</v>
+        <v>0.1294041728198898</v>
       </c>
       <c r="C72">
-        <v>84.25803630327943</v>
+        <v>82.96620314193314</v>
       </c>
       <c r="D72">
-        <v>184.9380363032794</v>
+        <v>185.1582031419331</v>
       </c>
       <c r="E72">
-        <v>68.54000000000001</v>
+        <v>70.05200000000001</v>
       </c>
       <c r="F72">
-        <v>105.84</v>
+        <v>107.352</v>
       </c>
       <c r="G72">
         <v>5.16</v>
@@ -7179,28 +7179,28 @@
         <v>18.825</v>
       </c>
       <c r="M72">
-        <v>8.022672000000002</v>
+        <v>8.137281600000001</v>
       </c>
       <c r="N72">
-        <v>10.802328</v>
+        <v>10.6877184</v>
       </c>
       <c r="O72">
-        <v>2.592558719999999</v>
+        <v>2.565052415999999</v>
       </c>
       <c r="P72">
-        <v>8.209769279999998</v>
+        <v>8.122665983999998</v>
       </c>
       <c r="Q72">
-        <v>16.00976928</v>
+        <v>15.922665984</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2972603424387186</v>
+        <v>0.3051810097237578</v>
       </c>
       <c r="T72">
-        <v>1.235518252212161</v>
+        <v>1.274435438538473</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.346475089596084</v>
+        <v>2.313426144672196</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1294041728198898</v>
+        <v>0.1293046429081639</v>
       </c>
       <c r="C73">
-        <v>82.96620314193315</v>
+        <v>81.67489481813486</v>
       </c>
       <c r="D73">
-        <v>185.1582031419331</v>
+        <v>185.3788948181349</v>
       </c>
       <c r="E73">
-        <v>70.05199999999999</v>
+        <v>71.56399999999999</v>
       </c>
       <c r="F73">
-        <v>107.352</v>
+        <v>108.864</v>
       </c>
       <c r="G73">
         <v>5.16</v>
@@ -7261,28 +7261,28 @@
         <v>18.825</v>
       </c>
       <c r="M73">
-        <v>8.1372816</v>
+        <v>8.251891199999999</v>
       </c>
       <c r="N73">
-        <v>10.6877184</v>
+        <v>10.5731088</v>
       </c>
       <c r="O73">
-        <v>2.565052416</v>
+        <v>2.537546112</v>
       </c>
       <c r="P73">
-        <v>8.122665983999999</v>
+        <v>8.035562688000001</v>
       </c>
       <c r="Q73">
-        <v>15.922665984</v>
+        <v>15.835562688</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3051810097237577</v>
+        <v>0.3136674389577283</v>
       </c>
       <c r="T73">
-        <v>1.274435438538473</v>
+        <v>1.316132423888092</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.313426144672196</v>
+        <v>2.281295225996193</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1293046429081639</v>
+        <v>0.1292051129964381</v>
       </c>
       <c r="C74">
-        <v>81.67489481813486</v>
+        <v>80.38411321079938</v>
       </c>
       <c r="D74">
-        <v>185.3788948181349</v>
+        <v>185.6001132107994</v>
       </c>
       <c r="E74">
-        <v>71.56399999999999</v>
+        <v>73.07599999999999</v>
       </c>
       <c r="F74">
-        <v>108.864</v>
+        <v>110.376</v>
       </c>
       <c r="G74">
         <v>5.16</v>
@@ -7343,28 +7343,28 @@
         <v>18.825</v>
       </c>
       <c r="M74">
-        <v>8.251891199999999</v>
+        <v>8.366500800000001</v>
       </c>
       <c r="N74">
-        <v>10.5731088</v>
+        <v>10.4584992</v>
       </c>
       <c r="O74">
-        <v>2.537546112</v>
+        <v>2.510039808</v>
       </c>
       <c r="P74">
-        <v>8.035562688000001</v>
+        <v>7.948459391999998</v>
       </c>
       <c r="Q74">
-        <v>15.835562688</v>
+        <v>15.748459392</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3136674389577283</v>
+        <v>0.3227824925794004</v>
       </c>
       <c r="T74">
-        <v>1.316132423888092</v>
+        <v>1.360918074819165</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.281295225996193</v>
+        <v>2.250044606461999</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1292051129964381</v>
+        <v>0.1291055830847123</v>
       </c>
       <c r="C75">
-        <v>80.38411321079938</v>
+        <v>79.09386020782109</v>
       </c>
       <c r="D75">
-        <v>185.6001132107994</v>
+        <v>185.8218602078211</v>
       </c>
       <c r="E75">
-        <v>73.07599999999999</v>
+        <v>74.58799999999999</v>
       </c>
       <c r="F75">
-        <v>110.376</v>
+        <v>111.888</v>
       </c>
       <c r="G75">
         <v>5.16</v>
@@ -7425,28 +7425,28 @@
         <v>18.825</v>
       </c>
       <c r="M75">
-        <v>8.366500800000001</v>
+        <v>8.4811104</v>
       </c>
       <c r="N75">
-        <v>10.4584992</v>
+        <v>10.3438896</v>
       </c>
       <c r="O75">
-        <v>2.510039808</v>
+        <v>2.482533504</v>
       </c>
       <c r="P75">
-        <v>7.948459391999998</v>
+        <v>7.861356096</v>
       </c>
       <c r="Q75">
-        <v>15.748459392</v>
+        <v>15.661356096</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3227824925794004</v>
+        <v>0.3325987041719703</v>
       </c>
       <c r="T75">
-        <v>1.360918074819165</v>
+        <v>1.409148775821858</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.250044606461999</v>
+        <v>2.219638598266567</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1291055830847123</v>
+        <v>0.1290060531729865</v>
       </c>
       <c r="C76">
-        <v>79.09386020782109</v>
+        <v>77.80413770612704</v>
       </c>
       <c r="D76">
-        <v>185.8218602078211</v>
+        <v>186.044137706127</v>
       </c>
       <c r="E76">
-        <v>74.58799999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F76">
-        <v>111.888</v>
+        <v>113.4</v>
       </c>
       <c r="G76">
         <v>5.16</v>
@@ -7507,28 +7507,28 @@
         <v>18.825</v>
       </c>
       <c r="M76">
-        <v>8.4811104</v>
+        <v>8.59572</v>
       </c>
       <c r="N76">
-        <v>10.3438896</v>
+        <v>10.22928</v>
       </c>
       <c r="O76">
-        <v>2.482533504</v>
+        <v>2.4550272</v>
       </c>
       <c r="P76">
-        <v>7.861356096</v>
+        <v>7.774252799999999</v>
       </c>
       <c r="Q76">
-        <v>15.661356096</v>
+        <v>15.5742528</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3325987041719703</v>
+        <v>0.343200212691946</v>
       </c>
       <c r="T76">
-        <v>1.409148775821858</v>
+        <v>1.461237932904768</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.219638598266567</v>
+        <v>2.190043416956346</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1290060531729865</v>
+        <v>0.1289065232612607</v>
       </c>
       <c r="C77">
-        <v>77.80413770612704</v>
+        <v>76.51494761173207</v>
       </c>
       <c r="D77">
-        <v>186.044137706127</v>
+        <v>186.2669476117321</v>
       </c>
       <c r="E77">
-        <v>76.09999999999999</v>
+        <v>77.61199999999999</v>
       </c>
       <c r="F77">
-        <v>113.4</v>
+        <v>114.912</v>
       </c>
       <c r="G77">
         <v>5.16</v>
@@ -7589,28 +7589,28 @@
         <v>18.825</v>
       </c>
       <c r="M77">
-        <v>8.59572</v>
+        <v>8.7103296</v>
       </c>
       <c r="N77">
-        <v>10.22928</v>
+        <v>10.1146704</v>
       </c>
       <c r="O77">
-        <v>2.4550272</v>
+        <v>2.427520896</v>
       </c>
       <c r="P77">
-        <v>7.774252799999999</v>
+        <v>7.687149504</v>
       </c>
       <c r="Q77">
-        <v>15.5742528</v>
+        <v>15.487149504</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.343200212691946</v>
+        <v>0.3546851802552528</v>
       </c>
       <c r="T77">
-        <v>1.461237932904768</v>
+        <v>1.517667853077919</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.190043416956346</v>
+        <v>2.16122705620692</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1289065232612607</v>
+        <v>0.1288069933495349</v>
       </c>
       <c r="C78">
-        <v>76.51494761173207</v>
+        <v>75.22629183979204</v>
       </c>
       <c r="D78">
-        <v>186.2669476117321</v>
+        <v>186.490291839792</v>
       </c>
       <c r="E78">
-        <v>77.61199999999999</v>
+        <v>79.124</v>
       </c>
       <c r="F78">
-        <v>114.912</v>
+        <v>116.424</v>
       </c>
       <c r="G78">
         <v>5.16</v>
@@ -7671,28 +7671,28 @@
         <v>18.825</v>
       </c>
       <c r="M78">
-        <v>8.7103296</v>
+        <v>8.824939199999999</v>
       </c>
       <c r="N78">
-        <v>10.1146704</v>
+        <v>10.0000608</v>
       </c>
       <c r="O78">
-        <v>2.427520896</v>
+        <v>2.400014592</v>
       </c>
       <c r="P78">
-        <v>7.687149504</v>
+        <v>7.600046208</v>
       </c>
       <c r="Q78">
-        <v>15.487149504</v>
+        <v>15.400046208</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3546851802552528</v>
+        <v>0.3671688406501515</v>
       </c>
       <c r="T78">
-        <v>1.517667853077919</v>
+        <v>1.579004722831345</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.16122705620692</v>
+        <v>2.133159172360077</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1288069933495349</v>
+        <v>0.128707463437809</v>
       </c>
       <c r="C79">
-        <v>75.22629183979204</v>
+        <v>73.93817231465981</v>
       </c>
       <c r="D79">
-        <v>186.490291839792</v>
+        <v>186.7141723146598</v>
       </c>
       <c r="E79">
-        <v>79.124</v>
+        <v>80.636</v>
       </c>
       <c r="F79">
-        <v>116.424</v>
+        <v>117.936</v>
       </c>
       <c r="G79">
         <v>5.16</v>
@@ -7753,28 +7753,28 @@
         <v>18.825</v>
       </c>
       <c r="M79">
-        <v>8.824939199999999</v>
+        <v>8.939548800000001</v>
       </c>
       <c r="N79">
-        <v>10.0000608</v>
+        <v>9.885451199999999</v>
       </c>
       <c r="O79">
-        <v>2.400014592</v>
+        <v>2.372508288</v>
       </c>
       <c r="P79">
-        <v>7.600046208</v>
+        <v>7.512942911999999</v>
       </c>
       <c r="Q79">
-        <v>15.400046208</v>
+        <v>15.312942912</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3671688406501515</v>
+        <v>0.3807873792627684</v>
       </c>
       <c r="T79">
-        <v>1.579004722831345</v>
+        <v>1.645917671653264</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.133159172360077</v>
+        <v>2.10581097784264</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.128707463437809</v>
+        <v>0.1286079335260832</v>
       </c>
       <c r="C80">
-        <v>73.93817231465981</v>
+        <v>72.65059096993973</v>
       </c>
       <c r="D80">
-        <v>186.7141723146598</v>
+        <v>186.9385909699397</v>
       </c>
       <c r="E80">
-        <v>80.636</v>
+        <v>82.148</v>
       </c>
       <c r="F80">
-        <v>117.936</v>
+        <v>119.448</v>
       </c>
       <c r="G80">
         <v>5.16</v>
@@ -7835,28 +7835,28 @@
         <v>18.825</v>
       </c>
       <c r="M80">
-        <v>8.939548800000001</v>
+        <v>9.0541584</v>
       </c>
       <c r="N80">
-        <v>9.885451199999999</v>
+        <v>9.770841599999999</v>
       </c>
       <c r="O80">
-        <v>2.372508288</v>
+        <v>2.345001984</v>
       </c>
       <c r="P80">
-        <v>7.512942911999999</v>
+        <v>7.425839615999999</v>
       </c>
       <c r="Q80">
-        <v>15.312942912</v>
+        <v>15.225839616</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3807873792627684</v>
+        <v>0.3957029215527774</v>
       </c>
       <c r="T80">
-        <v>1.645917671653264</v>
+        <v>1.719203282267747</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.10581097784264</v>
+        <v>2.079155142680075</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1286079335260832</v>
+        <v>0.1285084036143574</v>
       </c>
       <c r="C81">
-        <v>72.65059096993973</v>
+        <v>71.36354974854392</v>
       </c>
       <c r="D81">
-        <v>186.9385909699397</v>
+        <v>187.1635497485439</v>
       </c>
       <c r="E81">
-        <v>82.148</v>
+        <v>83.66</v>
       </c>
       <c r="F81">
-        <v>119.448</v>
+        <v>120.96</v>
       </c>
       <c r="G81">
         <v>5.16</v>
@@ -7917,28 +7917,28 @@
         <v>18.825</v>
       </c>
       <c r="M81">
-        <v>9.0541584</v>
+        <v>9.168768</v>
       </c>
       <c r="N81">
-        <v>9.770841599999999</v>
+        <v>9.656231999999999</v>
       </c>
       <c r="O81">
-        <v>2.345001984</v>
+        <v>2.31749568</v>
       </c>
       <c r="P81">
-        <v>7.425839615999999</v>
+        <v>7.338736319999999</v>
       </c>
       <c r="Q81">
-        <v>15.225839616</v>
+        <v>15.13873632</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3957029215527774</v>
+        <v>0.4121100180717872</v>
       </c>
       <c r="T81">
-        <v>1.719203282267747</v>
+        <v>1.799817453943678</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.079155142680075</v>
+        <v>2.053165703396574</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1285084036143574</v>
+        <v>0.1284088737026316</v>
       </c>
       <c r="C82">
-        <v>71.36354974854392</v>
+        <v>70.07705060274775</v>
       </c>
       <c r="D82">
-        <v>187.1635497485439</v>
+        <v>187.3890506027477</v>
       </c>
       <c r="E82">
-        <v>83.66</v>
+        <v>85.172</v>
       </c>
       <c r="F82">
-        <v>120.96</v>
+        <v>122.472</v>
       </c>
       <c r="G82">
         <v>5.16</v>
@@ -7999,28 +7999,28 @@
         <v>18.825</v>
       </c>
       <c r="M82">
-        <v>9.168768</v>
+        <v>9.2833776</v>
       </c>
       <c r="N82">
-        <v>9.656231999999999</v>
+        <v>9.5416224</v>
       </c>
       <c r="O82">
-        <v>2.31749568</v>
+        <v>2.289989376</v>
       </c>
       <c r="P82">
-        <v>7.338736319999999</v>
+        <v>7.251633024</v>
       </c>
       <c r="Q82">
-        <v>15.13873632</v>
+        <v>15.051633024</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4121100180717872</v>
+        <v>0.4302441773822717</v>
       </c>
       <c r="T82">
-        <v>1.799817453943678</v>
+        <v>1.888917327901285</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.053165703396574</v>
+        <v>2.027817978663283</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1284088737026316</v>
+        <v>0.1283093437909058</v>
       </c>
       <c r="C83">
-        <v>70.07705060274775</v>
+        <v>68.79109549424687</v>
       </c>
       <c r="D83">
-        <v>187.3890506027477</v>
+        <v>187.6150954942469</v>
       </c>
       <c r="E83">
-        <v>85.172</v>
+        <v>86.684</v>
       </c>
       <c r="F83">
-        <v>122.472</v>
+        <v>123.984</v>
       </c>
       <c r="G83">
         <v>5.16</v>
@@ -8081,28 +8081,28 @@
         <v>18.825</v>
       </c>
       <c r="M83">
-        <v>9.2833776</v>
+        <v>9.397987200000001</v>
       </c>
       <c r="N83">
-        <v>9.5416224</v>
+        <v>9.427012799999998</v>
       </c>
       <c r="O83">
-        <v>2.289989376</v>
+        <v>2.262483071999999</v>
       </c>
       <c r="P83">
-        <v>7.251633024</v>
+        <v>7.164529727999999</v>
       </c>
       <c r="Q83">
-        <v>15.051633024</v>
+        <v>14.964529728</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4302441773822717</v>
+        <v>0.4503932432828101</v>
       </c>
       <c r="T83">
-        <v>1.888917327901285</v>
+        <v>1.987917187854183</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.027817978663283</v>
+        <v>2.003088491118609</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1283093437909058</v>
+        <v>0.13716717387918</v>
       </c>
       <c r="C84">
-        <v>68.79109549424687</v>
+        <v>49.09025843903758</v>
       </c>
       <c r="D84">
-        <v>187.6150954942469</v>
+        <v>169.4262584390376</v>
       </c>
       <c r="E84">
-        <v>86.684</v>
+        <v>88.196</v>
       </c>
       <c r="F84">
-        <v>123.984</v>
+        <v>125.496</v>
       </c>
       <c r="G84">
         <v>5.16</v>
@@ -8163,45 +8163,45 @@
         <v>18.825</v>
       </c>
       <c r="M84">
-        <v>9.397987200000001</v>
+        <v>11.29464</v>
       </c>
       <c r="N84">
-        <v>9.427012799999998</v>
+        <v>7.53036</v>
       </c>
       <c r="O84">
-        <v>2.262483071999999</v>
+        <v>1.8072864</v>
       </c>
       <c r="P84">
-        <v>7.164529727999999</v>
+        <v>5.7230736</v>
       </c>
       <c r="Q84">
-        <v>14.964529728</v>
+        <v>13.5230736</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4503932432828101</v>
+        <v>0.4729127875245882</v>
       </c>
       <c r="T84">
-        <v>1.987917187854183</v>
+        <v>2.09856409015448</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.24</v>
       </c>
       <c r="W84">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.003088491118609</v>
+        <v>1.666719789209749</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.13716717387918</v>
+        <v>0.1371755639674542</v>
       </c>
       <c r="C85">
-        <v>49.09025843903758</v>
+        <v>47.56270174967177</v>
       </c>
       <c r="D85">
-        <v>169.4262584390376</v>
+        <v>169.4107017496718</v>
       </c>
       <c r="E85">
-        <v>88.196</v>
+        <v>89.708</v>
       </c>
       <c r="F85">
-        <v>125.496</v>
+        <v>127.008</v>
       </c>
       <c r="G85">
         <v>5.16</v>
@@ -8245,28 +8245,28 @@
         <v>18.825</v>
       </c>
       <c r="M85">
-        <v>11.29464</v>
+        <v>11.43072</v>
       </c>
       <c r="N85">
-        <v>7.53036</v>
+        <v>7.39428</v>
       </c>
       <c r="O85">
-        <v>1.8072864</v>
+        <v>1.7746272</v>
       </c>
       <c r="P85">
-        <v>5.7230736</v>
+        <v>5.6196528</v>
       </c>
       <c r="Q85">
-        <v>13.5230736</v>
+        <v>13.4196528</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4729127875245882</v>
+        <v>0.4982472747965888</v>
       </c>
       <c r="T85">
-        <v>2.09856409015448</v>
+        <v>2.223041855242315</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.666719789209749</v>
+        <v>1.646877886957252</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1371755639674542</v>
+        <v>0.1371839540557284</v>
       </c>
       <c r="C86">
-        <v>47.56270174967179</v>
+        <v>46.03514791686862</v>
       </c>
       <c r="D86">
-        <v>169.4107017496718</v>
+        <v>169.3951479168686</v>
       </c>
       <c r="E86">
-        <v>89.70799999999998</v>
+        <v>91.21999999999998</v>
       </c>
       <c r="F86">
-        <v>127.008</v>
+        <v>128.52</v>
       </c>
       <c r="G86">
         <v>5.16</v>
@@ -8327,28 +8327,28 @@
         <v>18.825</v>
       </c>
       <c r="M86">
-        <v>11.43072</v>
+        <v>11.5668</v>
       </c>
       <c r="N86">
-        <v>7.394280000000002</v>
+        <v>7.258200000000002</v>
       </c>
       <c r="O86">
-        <v>1.774627200000001</v>
+        <v>1.741968</v>
       </c>
       <c r="P86">
-        <v>5.619652800000002</v>
+        <v>5.516232000000002</v>
       </c>
       <c r="Q86">
-        <v>13.4196528</v>
+        <v>13.316232</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4982472747965884</v>
+        <v>0.5269596937048556</v>
       </c>
       <c r="T86">
-        <v>2.223041855242314</v>
+        <v>2.364116655675193</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.646877886957252</v>
+        <v>1.627502852993049</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1371839540557284</v>
+        <v>0.1371923441440025</v>
       </c>
       <c r="C87">
-        <v>46.03514791686862</v>
+        <v>44.50759693984151</v>
       </c>
       <c r="D87">
-        <v>169.3951479168686</v>
+        <v>169.3795969398415</v>
       </c>
       <c r="E87">
-        <v>91.21999999999998</v>
+        <v>92.73199999999999</v>
       </c>
       <c r="F87">
-        <v>128.52</v>
+        <v>130.032</v>
       </c>
       <c r="G87">
         <v>5.16</v>
@@ -8409,28 +8409,28 @@
         <v>18.825</v>
       </c>
       <c r="M87">
-        <v>11.5668</v>
+        <v>11.70288</v>
       </c>
       <c r="N87">
-        <v>7.258200000000002</v>
+        <v>7.122120000000001</v>
       </c>
       <c r="O87">
-        <v>1.741968</v>
+        <v>1.7093088</v>
       </c>
       <c r="P87">
-        <v>5.516232000000002</v>
+        <v>5.4128112</v>
       </c>
       <c r="Q87">
-        <v>13.316232</v>
+        <v>13.2128112</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5269596937048556</v>
+        <v>0.5597738867428751</v>
       </c>
       <c r="T87">
-        <v>2.364116655675193</v>
+        <v>2.525344999027054</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.627502852993049</v>
+        <v>1.60857840121406</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1371923441440025</v>
+        <v>0.1372007342322767</v>
       </c>
       <c r="C88">
-        <v>44.50759693984151</v>
+        <v>42.98004881780389</v>
       </c>
       <c r="D88">
-        <v>169.3795969398415</v>
+        <v>169.3640488178039</v>
       </c>
       <c r="E88">
-        <v>92.73199999999999</v>
+        <v>94.24399999999999</v>
       </c>
       <c r="F88">
-        <v>130.032</v>
+        <v>131.544</v>
       </c>
       <c r="G88">
         <v>5.16</v>
@@ -8491,28 +8491,28 @@
         <v>18.825</v>
       </c>
       <c r="M88">
-        <v>11.70288</v>
+        <v>11.83896</v>
       </c>
       <c r="N88">
-        <v>7.122120000000001</v>
+        <v>6.986040000000001</v>
       </c>
       <c r="O88">
-        <v>1.7093088</v>
+        <v>1.6766496</v>
       </c>
       <c r="P88">
-        <v>5.4128112</v>
+        <v>5.309390400000001</v>
       </c>
       <c r="Q88">
-        <v>13.2128112</v>
+        <v>13.1093904</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5597738867428751</v>
+        <v>0.5976364171713593</v>
       </c>
       <c r="T88">
-        <v>2.525344999027054</v>
+        <v>2.711377702894588</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.60857840121406</v>
+        <v>1.590088994303554</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1372007342322767</v>
+        <v>0.1372091243205509</v>
       </c>
       <c r="C89">
-        <v>42.98004881780389</v>
+        <v>41.45250354996966</v>
       </c>
       <c r="D89">
-        <v>169.3640488178039</v>
+        <v>169.3485035499696</v>
       </c>
       <c r="E89">
-        <v>94.24399999999999</v>
+        <v>95.75599999999999</v>
       </c>
       <c r="F89">
-        <v>131.544</v>
+        <v>133.056</v>
       </c>
       <c r="G89">
         <v>5.16</v>
@@ -8573,28 +8573,28 @@
         <v>18.825</v>
       </c>
       <c r="M89">
-        <v>11.83896</v>
+        <v>11.97504</v>
       </c>
       <c r="N89">
-        <v>6.986040000000001</v>
+        <v>6.849960000000001</v>
       </c>
       <c r="O89">
-        <v>1.6766496</v>
+        <v>1.6439904</v>
       </c>
       <c r="P89">
-        <v>5.309390400000001</v>
+        <v>5.205969600000001</v>
       </c>
       <c r="Q89">
-        <v>13.1093904</v>
+        <v>13.0059696</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5976364171713593</v>
+        <v>0.6418093693379242</v>
       </c>
       <c r="T89">
-        <v>2.711377702894588</v>
+        <v>2.928415857406709</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.590088994303554</v>
+        <v>1.572019801186468</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1372091243205509</v>
+        <v>0.1372175144088251</v>
       </c>
       <c r="C90">
-        <v>41.45250354996966</v>
+        <v>39.92496113555296</v>
       </c>
       <c r="D90">
-        <v>169.3485035499696</v>
+        <v>169.3329611355529</v>
       </c>
       <c r="E90">
-        <v>95.75599999999999</v>
+        <v>97.26799999999999</v>
       </c>
       <c r="F90">
-        <v>133.056</v>
+        <v>134.568</v>
       </c>
       <c r="G90">
         <v>5.16</v>
@@ -8655,28 +8655,28 @@
         <v>18.825</v>
       </c>
       <c r="M90">
-        <v>11.97504</v>
+        <v>12.11112</v>
       </c>
       <c r="N90">
-        <v>6.849960000000001</v>
+        <v>6.713880000000001</v>
       </c>
       <c r="O90">
-        <v>1.6439904</v>
+        <v>1.6113312</v>
       </c>
       <c r="P90">
-        <v>5.205969600000001</v>
+        <v>5.102548800000001</v>
       </c>
       <c r="Q90">
-        <v>13.0059696</v>
+        <v>12.9025488</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6418093693379242</v>
+        <v>0.6940137673529554</v>
       </c>
       <c r="T90">
-        <v>2.928415857406709</v>
+        <v>3.184915494557398</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.572019801186468</v>
+        <v>1.554356657352912</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1372175144088251</v>
+        <v>0.1372259044970993</v>
       </c>
       <c r="C91">
-        <v>39.92496113555296</v>
+        <v>38.39742157376827</v>
       </c>
       <c r="D91">
-        <v>169.3329611355529</v>
+        <v>169.3174215737683</v>
       </c>
       <c r="E91">
-        <v>97.26799999999999</v>
+        <v>98.77999999999999</v>
       </c>
       <c r="F91">
-        <v>134.568</v>
+        <v>136.08</v>
       </c>
       <c r="G91">
         <v>5.16</v>
@@ -8737,28 +8737,28 @@
         <v>18.825</v>
       </c>
       <c r="M91">
-        <v>12.11112</v>
+        <v>12.2472</v>
       </c>
       <c r="N91">
-        <v>6.713880000000001</v>
+        <v>6.577800000000002</v>
       </c>
       <c r="O91">
-        <v>1.6113312</v>
+        <v>1.578672</v>
       </c>
       <c r="P91">
-        <v>5.102548800000001</v>
+        <v>4.999128000000002</v>
       </c>
       <c r="Q91">
-        <v>12.9025488</v>
+        <v>12.799128</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6940137673529554</v>
+        <v>0.7566590449709928</v>
       </c>
       <c r="T91">
-        <v>3.184915494557398</v>
+        <v>3.492715059138225</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.554356657352912</v>
+        <v>1.537086027826769</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1372259044970993</v>
+        <v>0.1372342945853735</v>
       </c>
       <c r="C92">
-        <v>38.39742157376827</v>
+        <v>36.86988486383024</v>
       </c>
       <c r="D92">
-        <v>169.3174215737683</v>
+        <v>169.3018848638302</v>
       </c>
       <c r="E92">
-        <v>98.77999999999999</v>
+        <v>100.292</v>
       </c>
       <c r="F92">
-        <v>136.08</v>
+        <v>137.592</v>
       </c>
       <c r="G92">
         <v>5.16</v>
@@ -8819,28 +8819,28 @@
         <v>18.825</v>
       </c>
       <c r="M92">
-        <v>12.2472</v>
+        <v>12.38328</v>
       </c>
       <c r="N92">
-        <v>6.577800000000002</v>
+        <v>6.441720000000002</v>
       </c>
       <c r="O92">
-        <v>1.578672</v>
+        <v>1.5460128</v>
       </c>
       <c r="P92">
-        <v>4.999128000000002</v>
+        <v>4.895707200000001</v>
       </c>
       <c r="Q92">
-        <v>12.799128</v>
+        <v>12.6957072</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7566590449709928</v>
+        <v>0.8332254953930386</v>
       </c>
       <c r="T92">
-        <v>3.492715059138225</v>
+        <v>3.868914526959236</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.537086027826769</v>
+        <v>1.520194972575925</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1372342945853735</v>
+        <v>0.1372426846736476</v>
       </c>
       <c r="C93">
-        <v>36.86988486383024</v>
+        <v>35.34235100495391</v>
       </c>
       <c r="D93">
-        <v>169.3018848638302</v>
+        <v>169.2863510049539</v>
       </c>
       <c r="E93">
-        <v>100.292</v>
+        <v>101.804</v>
       </c>
       <c r="F93">
-        <v>137.592</v>
+        <v>139.104</v>
       </c>
       <c r="G93">
         <v>5.16</v>
@@ -8901,28 +8901,28 @@
         <v>18.825</v>
       </c>
       <c r="M93">
-        <v>12.38328</v>
+        <v>12.51936</v>
       </c>
       <c r="N93">
-        <v>6.441720000000002</v>
+        <v>6.30564</v>
       </c>
       <c r="O93">
-        <v>1.5460128</v>
+        <v>1.5133536</v>
       </c>
       <c r="P93">
-        <v>4.895707200000001</v>
+        <v>4.7922864</v>
       </c>
       <c r="Q93">
-        <v>12.6957072</v>
+        <v>12.5922864</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8332254953930386</v>
+        <v>0.9289335584205959</v>
       </c>
       <c r="T93">
-        <v>3.868914526959236</v>
+        <v>4.339163861735501</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.520194972575925</v>
+        <v>1.503671114178361</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1372426846736476</v>
+        <v>0.1820639194158438</v>
       </c>
       <c r="C94">
-        <v>35.34235100495391</v>
+        <v>-21.85293852297535</v>
       </c>
       <c r="D94">
-        <v>169.2863510049539</v>
+        <v>113.6030614770246</v>
       </c>
       <c r="E94">
-        <v>101.804</v>
+        <v>103.316</v>
       </c>
       <c r="F94">
-        <v>139.104</v>
+        <v>140.616</v>
       </c>
       <c r="G94">
         <v>5.16</v>
@@ -8983,45 +8983,45 @@
         <v>18.825</v>
       </c>
       <c r="M94">
-        <v>12.51936</v>
+        <v>20.6424288</v>
       </c>
       <c r="N94">
-        <v>6.30564</v>
+        <v>-1.817428800000002</v>
       </c>
       <c r="O94">
-        <v>1.5133536</v>
+        <v>-0.4361829120000004</v>
       </c>
       <c r="P94">
-        <v>4.7922864</v>
+        <v>-1.381245888000001</v>
       </c>
       <c r="Q94">
-        <v>12.5922864</v>
+        <v>6.418754111999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9289335584205959</v>
+        <v>1.077441025668517</v>
       </c>
       <c r="T94">
-        <v>4.339163861735501</v>
+        <v>5.068836320601738</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.24</v>
+        <v>0.2188695934850457</v>
       </c>
       <c r="W94">
-        <v>0.0684</v>
+        <v>0.1146699436763953</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.503671114178361</v>
+        <v>0.9119566395210237</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1820639194158438</v>
+        <v>0.1830739194158437</v>
       </c>
       <c r="C95">
-        <v>-21.85293852297535</v>
+        <v>-24.2007789548655</v>
       </c>
       <c r="D95">
-        <v>113.6030614770246</v>
+        <v>112.7672210451345</v>
       </c>
       <c r="E95">
-        <v>103.316</v>
+        <v>104.828</v>
       </c>
       <c r="F95">
-        <v>140.616</v>
+        <v>142.128</v>
       </c>
       <c r="G95">
         <v>5.16</v>
@@ -9065,37 +9065,37 @@
         <v>18.825</v>
       </c>
       <c r="M95">
-        <v>20.6424288</v>
+        <v>20.8643904</v>
       </c>
       <c r="N95">
-        <v>-1.817428800000002</v>
+        <v>-2.039390400000002</v>
       </c>
       <c r="O95">
-        <v>-0.4361829120000004</v>
+        <v>-0.4894536960000005</v>
       </c>
       <c r="P95">
-        <v>-1.381245888000001</v>
+        <v>-1.549936704000002</v>
       </c>
       <c r="Q95">
-        <v>6.418754111999999</v>
+        <v>6.250063295999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.077441025668517</v>
+        <v>1.24938119661327</v>
       </c>
       <c r="T95">
-        <v>5.068836320601738</v>
+        <v>5.913642374035362</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2188695934850457</v>
+        <v>0.2165411935543537</v>
       </c>
       <c r="W95">
-        <v>0.1146699436763953</v>
+        <v>0.1150117527862209</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9119566395210237</v>
+        <v>0.9022549731431405</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1830739194158437</v>
+        <v>0.1840839194158438</v>
       </c>
       <c r="C96">
-        <v>-24.2007789548655</v>
+        <v>-26.5364097409809</v>
       </c>
       <c r="D96">
-        <v>112.7672210451345</v>
+        <v>111.9435902590191</v>
       </c>
       <c r="E96">
-        <v>104.828</v>
+        <v>106.34</v>
       </c>
       <c r="F96">
-        <v>142.128</v>
+        <v>143.64</v>
       </c>
       <c r="G96">
         <v>5.16</v>
@@ -9147,37 +9147,37 @@
         <v>18.825</v>
       </c>
       <c r="M96">
-        <v>20.8643904</v>
+        <v>21.086352</v>
       </c>
       <c r="N96">
-        <v>-2.039390400000002</v>
+        <v>-2.261352000000002</v>
       </c>
       <c r="O96">
-        <v>-0.4894536960000005</v>
+        <v>-0.5427244800000005</v>
       </c>
       <c r="P96">
-        <v>-1.549936704000002</v>
+        <v>-1.718627520000002</v>
       </c>
       <c r="Q96">
-        <v>6.250063295999999</v>
+        <v>6.081372479999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.24938119661327</v>
+        <v>1.490097435935924</v>
       </c>
       <c r="T96">
-        <v>5.913642374035362</v>
+        <v>7.096370848842438</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2165411935543537</v>
+        <v>0.214261812569571</v>
       </c>
       <c r="W96">
-        <v>0.1150117527862209</v>
+        <v>0.115346365914787</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9022549731431405</v>
+        <v>0.8927575523732126</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1840839194158438</v>
+        <v>0.1850939194158438</v>
       </c>
       <c r="C97">
-        <v>-26.5364097409809</v>
+        <v>-28.86009647243164</v>
       </c>
       <c r="D97">
-        <v>111.9435902590191</v>
+        <v>111.1319035275684</v>
       </c>
       <c r="E97">
-        <v>106.34</v>
+        <v>107.852</v>
       </c>
       <c r="F97">
-        <v>143.64</v>
+        <v>145.152</v>
       </c>
       <c r="G97">
         <v>5.16</v>
@@ -9229,37 +9229,37 @@
         <v>18.825</v>
       </c>
       <c r="M97">
-        <v>21.086352</v>
+        <v>21.3083136</v>
       </c>
       <c r="N97">
-        <v>-2.261352000000002</v>
+        <v>-2.483313600000002</v>
       </c>
       <c r="O97">
-        <v>-0.5427244800000005</v>
+        <v>-0.5959952640000006</v>
       </c>
       <c r="P97">
-        <v>-1.718627520000002</v>
+        <v>-1.887318336000002</v>
       </c>
       <c r="Q97">
-        <v>6.081372479999999</v>
+        <v>5.912681663999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.490097435935924</v>
+        <v>1.851171794919906</v>
       </c>
       <c r="T97">
-        <v>7.096370848842438</v>
+        <v>8.870463561053052</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.214261812569571</v>
+        <v>0.212029918688638</v>
       </c>
       <c r="W97">
-        <v>0.115346365914787</v>
+        <v>0.115674007936508</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8927575523732126</v>
+        <v>0.8834579945359917</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1850939194158438</v>
+        <v>0.1861039194158438</v>
       </c>
       <c r="C98">
-        <v>-28.86009647243164</v>
+        <v>-31.1720970927291</v>
       </c>
       <c r="D98">
-        <v>111.1319035275684</v>
+        <v>110.3319029072709</v>
       </c>
       <c r="E98">
-        <v>107.852</v>
+        <v>109.364</v>
       </c>
       <c r="F98">
-        <v>145.152</v>
+        <v>146.664</v>
       </c>
       <c r="G98">
         <v>5.16</v>
@@ -9311,37 +9311,37 @@
         <v>18.825</v>
       </c>
       <c r="M98">
-        <v>21.3083136</v>
+        <v>21.5302752</v>
       </c>
       <c r="N98">
-        <v>-2.483313600000002</v>
+        <v>-2.705275199999999</v>
       </c>
       <c r="O98">
-        <v>-0.5959952640000006</v>
+        <v>-0.6492660479999998</v>
       </c>
       <c r="P98">
-        <v>-1.887318336000002</v>
+        <v>-2.056009151999999</v>
       </c>
       <c r="Q98">
-        <v>5.912681663999999</v>
+        <v>5.743990848000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.851171794919902</v>
+        <v>2.452962393226535</v>
       </c>
       <c r="T98">
-        <v>8.870463561053029</v>
+        <v>11.8272847480707</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.212029918688638</v>
+        <v>0.2098440432382397</v>
       </c>
       <c r="W98">
-        <v>0.115674007936508</v>
+        <v>0.1159948944526264</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8834579945359917</v>
+        <v>0.8743501801593321</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1861039194158438</v>
+        <v>0.1871139194158437</v>
       </c>
       <c r="C99">
-        <v>-31.1720970927291</v>
+        <v>-33.47266217108081</v>
       </c>
       <c r="D99">
-        <v>110.3319029072709</v>
+        <v>109.5433378289192</v>
       </c>
       <c r="E99">
-        <v>109.364</v>
+        <v>110.876</v>
       </c>
       <c r="F99">
-        <v>146.664</v>
+        <v>148.176</v>
       </c>
       <c r="G99">
         <v>5.16</v>
@@ -9393,37 +9393,37 @@
         <v>18.825</v>
       </c>
       <c r="M99">
-        <v>21.5302752</v>
+        <v>21.7522368</v>
       </c>
       <c r="N99">
-        <v>-2.705275199999999</v>
+        <v>-2.927236799999999</v>
       </c>
       <c r="O99">
-        <v>-0.6492660479999998</v>
+        <v>-0.7025368319999998</v>
       </c>
       <c r="P99">
-        <v>-2.056009151999999</v>
+        <v>-2.224699967999999</v>
       </c>
       <c r="Q99">
-        <v>5.743990848000001</v>
+        <v>5.575300032000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.452962393226535</v>
+        <v>3.656543589839802</v>
       </c>
       <c r="T99">
-        <v>11.8272847480707</v>
+        <v>17.74092712210605</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2098440432382397</v>
+        <v>0.2077027774909107</v>
       </c>
       <c r="W99">
-        <v>0.1159948944526264</v>
+        <v>0.1163092322643343</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8743501801593321</v>
+        <v>0.8654282395454613</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1871139194158437</v>
+        <v>0.1881239194158437</v>
       </c>
       <c r="C100">
-        <v>-33.47266217108081</v>
+        <v>-35.76203516404865</v>
       </c>
       <c r="D100">
-        <v>109.5433378289192</v>
+        <v>108.7659648359513</v>
       </c>
       <c r="E100">
-        <v>110.876</v>
+        <v>112.388</v>
       </c>
       <c r="F100">
-        <v>148.176</v>
+        <v>149.688</v>
       </c>
       <c r="G100">
         <v>5.16</v>
@@ -9475,37 +9475,37 @@
         <v>18.825</v>
       </c>
       <c r="M100">
-        <v>21.7522368</v>
+        <v>21.9741984</v>
       </c>
       <c r="N100">
-        <v>-2.927236799999999</v>
+        <v>-3.1491984</v>
       </c>
       <c r="O100">
-        <v>-0.7025368319999998</v>
+        <v>-0.7558076159999999</v>
       </c>
       <c r="P100">
-        <v>-2.224699967999999</v>
+        <v>-2.393390784</v>
       </c>
       <c r="Q100">
-        <v>5.575300032000001</v>
+        <v>5.406609216000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.656543589839802</v>
+        <v>7.267287179679605</v>
       </c>
       <c r="T100">
-        <v>17.74092712210605</v>
+        <v>35.48185424421211</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2077027774909107</v>
+        <v>0.2056047696374672</v>
       </c>
       <c r="W100">
-        <v>0.1163092322643343</v>
+        <v>0.1166172198172198</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8654282395454613</v>
+        <v>0.8566865401561132</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1881239194158437</v>
-      </c>
-      <c r="C101">
-        <v>-35.76203516404865</v>
-      </c>
-      <c r="D101">
-        <v>108.7659648359513</v>
-      </c>
-      <c r="E101">
-        <v>112.388</v>
-      </c>
-      <c r="F101">
-        <v>149.688</v>
-      </c>
-      <c r="G101">
-        <v>5.16</v>
-      </c>
-      <c r="H101">
-        <v>113.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>26.625</v>
-      </c>
-      <c r="K101">
-        <v>7.800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>18.825</v>
-      </c>
-      <c r="M101">
-        <v>21.9741984</v>
-      </c>
-      <c r="N101">
-        <v>-3.1491984</v>
-      </c>
-      <c r="O101">
-        <v>-0.7558076159999999</v>
-      </c>
-      <c r="P101">
-        <v>-2.393390784</v>
-      </c>
-      <c r="Q101">
-        <v>5.406609216000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.267287179679605</v>
-      </c>
-      <c r="T101">
-        <v>35.48185424421211</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2056047696374672</v>
-      </c>
-      <c r="W101">
-        <v>0.1166172198172198</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8566865401561132</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
